--- a/InputData/trans/SYVbT/Start Year Vehicles by Technology.xlsx
+++ b/InputData/trans/SYVbT/Start Year Vehicles by Technology.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28724"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/skorpius/My Drive/2024/FO local_EPS ICM/Diario/20250317_Trans2/SYVbT/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rachel Goldstein\Desktop\EPS Models\Mexico EPS\InputData\trans\SYVbT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BD269E4-816B-D44A-BE9F-8FB83E17342C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9ADCFEE3-EE4F-421D-9E7F-B8BB47F83F39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-8080" yWindow="-21100" windowWidth="32480" windowHeight="20120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="44145" yWindow="1230" windowWidth="22785" windowHeight="14115" firstSheet="2" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -4175,7 +4175,7 @@
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="63" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="105">
+  <cellXfs count="106">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -4361,12 +4361,15 @@
     <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="63" fillId="37" borderId="0" xfId="147" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="10" fontId="63" fillId="37" borderId="0" xfId="147" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="49" fillId="2" borderId="0" xfId="73" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="60" fillId="36" borderId="0" xfId="73" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="73" applyFont="1"/>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="21" xfId="73" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="57" fillId="35" borderId="23" xfId="73" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -4406,9 +4409,7 @@
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="21" xfId="73" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="73" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="148">
     <cellStyle name="20% - Accent1 2" xfId="15" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -5663,9 +5664,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B38"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="73.140625" customWidth="1"/>
+    <col min="2" max="2" width="73.109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -5848,15 +5849,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA9ECEC9-2D67-2F44-9D1D-E497A821C590}">
   <dimension ref="A1:AU81"/>
-  <sheetFormatPr defaultColWidth="10.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="10.88671875" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="30.85546875" style="69" customWidth="1"/>
-    <col min="2" max="2" width="11.140625" style="69" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.85546875" style="69"/>
-    <col min="4" max="4" width="13.7109375" style="69" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="11.140625" style="69" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="30.88671875" style="69" customWidth="1"/>
+    <col min="2" max="2" width="11.109375" style="69" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.88671875" style="69"/>
+    <col min="4" max="4" width="13.6640625" style="69" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="11.109375" style="69" bestFit="1" customWidth="1"/>
     <col min="7" max="8" width="11" style="69" bestFit="1" customWidth="1"/>
-    <col min="9" max="16384" width="10.85546875" style="69"/>
+    <col min="9" max="16384" width="10.88671875" style="69"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:47">
@@ -7291,7 +7292,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="61" spans="1:11" ht="15.95">
+    <row r="61" spans="1:11">
       <c r="A61" s="23" t="s">
         <v>97</v>
       </c>
@@ -7452,7 +7453,7 @@
         <v>8.8161936993136521E-4</v>
       </c>
       <c r="C69" s="69">
-        <f t="shared" ref="B69:H69" si="5">C60</f>
+        <f t="shared" ref="C69:H69" si="5">C60</f>
         <v>2.9494640303658694E-4</v>
       </c>
       <c r="D69" s="69">
@@ -7472,7 +7473,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:44" ht="15.95">
+    <row r="70" spans="1:44">
       <c r="A70" s="23" t="s">
         <v>97</v>
       </c>
@@ -7885,7 +7886,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{847F86A9-3044-3740-AA01-A50E40D8D85E}">
   <dimension ref="B26:F30"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="26" spans="2:6">
       <c r="B26" t="s">
@@ -7937,15 +7938,15 @@
     <tabColor theme="1" tint="0.34998626667073579"/>
   </sheetPr>
   <dimension ref="A2:AL409"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="14.1"/>
+  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="2" width="2" style="32" customWidth="1"/>
-    <col min="3" max="3" width="23.140625" style="32" customWidth="1"/>
+    <col min="3" max="3" width="23.109375" style="32" customWidth="1"/>
     <col min="4" max="4" width="33" style="32" bestFit="1" customWidth="1"/>
-    <col min="5" max="36" width="6.28515625" style="32" customWidth="1"/>
-    <col min="37" max="37" width="7.7109375" style="32" customWidth="1"/>
+    <col min="5" max="36" width="6.33203125" style="32" customWidth="1"/>
+    <col min="37" max="37" width="7.6640625" style="32" customWidth="1"/>
     <col min="38" max="38" width="2" style="32" customWidth="1"/>
-    <col min="39" max="16384" width="11.42578125" style="32"/>
+    <col min="39" max="16384" width="11.44140625" style="32"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:38">
@@ -8223,46 +8224,46 @@
       </c>
     </row>
     <row r="5" spans="1:38" ht="13.5" customHeight="1">
-      <c r="A5" s="90" t="s">
+      <c r="A5" s="93" t="s">
         <v>114</v>
       </c>
-      <c r="B5" s="90"/>
-      <c r="C5" s="90"/>
-      <c r="D5" s="90"/>
-      <c r="E5" s="90"/>
-      <c r="F5" s="90"/>
-      <c r="G5" s="90"/>
-      <c r="H5" s="90"/>
-      <c r="I5" s="90"/>
-      <c r="J5" s="90"/>
-      <c r="K5" s="90"/>
-      <c r="L5" s="90"/>
-      <c r="M5" s="90"/>
-      <c r="N5" s="90"/>
-      <c r="O5" s="90"/>
-      <c r="P5" s="90"/>
-      <c r="Q5" s="90"/>
-      <c r="R5" s="90"/>
-      <c r="S5" s="90"/>
-      <c r="T5" s="90"/>
-      <c r="U5" s="90"/>
-      <c r="V5" s="90"/>
-      <c r="W5" s="90"/>
-      <c r="X5" s="90"/>
-      <c r="Y5" s="90"/>
-      <c r="Z5" s="90"/>
-      <c r="AA5" s="90"/>
-      <c r="AB5" s="90"/>
-      <c r="AC5" s="90"/>
-      <c r="AD5" s="90"/>
-      <c r="AE5" s="90"/>
-      <c r="AF5" s="90"/>
-      <c r="AG5" s="90"/>
-      <c r="AH5" s="90"/>
-      <c r="AI5" s="90"/>
-      <c r="AJ5" s="90"/>
-      <c r="AK5" s="90"/>
-      <c r="AL5" s="90"/>
+      <c r="B5" s="93"/>
+      <c r="C5" s="93"/>
+      <c r="D5" s="93"/>
+      <c r="E5" s="93"/>
+      <c r="F5" s="93"/>
+      <c r="G5" s="93"/>
+      <c r="H5" s="93"/>
+      <c r="I5" s="93"/>
+      <c r="J5" s="93"/>
+      <c r="K5" s="93"/>
+      <c r="L5" s="93"/>
+      <c r="M5" s="93"/>
+      <c r="N5" s="93"/>
+      <c r="O5" s="93"/>
+      <c r="P5" s="93"/>
+      <c r="Q5" s="93"/>
+      <c r="R5" s="93"/>
+      <c r="S5" s="93"/>
+      <c r="T5" s="93"/>
+      <c r="U5" s="93"/>
+      <c r="V5" s="93"/>
+      <c r="W5" s="93"/>
+      <c r="X5" s="93"/>
+      <c r="Y5" s="93"/>
+      <c r="Z5" s="93"/>
+      <c r="AA5" s="93"/>
+      <c r="AB5" s="93"/>
+      <c r="AC5" s="93"/>
+      <c r="AD5" s="93"/>
+      <c r="AE5" s="93"/>
+      <c r="AF5" s="93"/>
+      <c r="AG5" s="93"/>
+      <c r="AH5" s="93"/>
+      <c r="AI5" s="93"/>
+      <c r="AJ5" s="93"/>
+      <c r="AK5" s="93"/>
+      <c r="AL5" s="93"/>
     </row>
     <row r="6" spans="1:38" ht="13.5" customHeight="1" thickBot="1"/>
     <row r="7" spans="1:38" s="62" customFormat="1" ht="22.5" customHeight="1" thickTop="1" thickBot="1">
@@ -8375,10 +8376,10 @@
     </row>
     <row r="8" spans="1:38" s="62" customFormat="1" ht="21" customHeight="1" thickTop="1">
       <c r="B8" s="61"/>
-      <c r="C8" s="91" t="s">
+      <c r="C8" s="94" t="s">
         <v>117</v>
       </c>
-      <c r="D8" s="91"/>
+      <c r="D8" s="94"/>
       <c r="E8" s="60">
         <f t="shared" ref="E8:AJ8" si="2">+E9+E14+E23+E18+E40+E42+E62+E75+E79+E82+E95+E102+E119+E121</f>
         <v>130</v>
@@ -8514,10 +8515,10 @@
     </row>
     <row r="9" spans="1:38" s="62" customFormat="1" ht="19.5" customHeight="1">
       <c r="B9" s="55"/>
-      <c r="C9" s="87" t="s">
+      <c r="C9" s="88" t="s">
         <v>118</v>
       </c>
-      <c r="D9" s="87"/>
+      <c r="D9" s="88"/>
       <c r="E9" s="54"/>
       <c r="F9" s="54"/>
       <c r="G9" s="54"/>
@@ -8818,10 +8819,10 @@
       <c r="B14" s="55">
         <v>5</v>
       </c>
-      <c r="C14" s="87" t="s">
+      <c r="C14" s="88" t="s">
         <v>123</v>
       </c>
-      <c r="D14" s="87"/>
+      <c r="D14" s="88"/>
       <c r="E14" s="54"/>
       <c r="F14" s="54"/>
       <c r="G14" s="54"/>
@@ -9044,10 +9045,10 @@
     </row>
     <row r="18" spans="2:37" ht="19.5" customHeight="1">
       <c r="B18" s="55"/>
-      <c r="C18" s="87" t="s">
+      <c r="C18" s="88" t="s">
         <v>127</v>
       </c>
-      <c r="D18" s="87"/>
+      <c r="D18" s="88"/>
       <c r="E18" s="54">
         <f t="shared" ref="E18:V18" si="5">SUM(E19:E22)</f>
         <v>10</v>
@@ -9384,10 +9385,10 @@
       <c r="B23" s="55">
         <v>3</v>
       </c>
-      <c r="C23" s="87" t="s">
+      <c r="C23" s="88" t="s">
         <v>132</v>
       </c>
-      <c r="D23" s="87"/>
+      <c r="D23" s="88"/>
       <c r="E23" s="54"/>
       <c r="F23" s="54"/>
       <c r="G23" s="54"/>
@@ -10268,10 +10269,10 @@
     </row>
     <row r="40" spans="2:37" ht="19.5" customHeight="1">
       <c r="B40" s="55"/>
-      <c r="C40" s="87" t="s">
+      <c r="C40" s="88" t="s">
         <v>149</v>
       </c>
-      <c r="D40" s="87"/>
+      <c r="D40" s="88"/>
       <c r="E40" s="54"/>
       <c r="F40" s="54"/>
       <c r="G40" s="54"/>
@@ -10365,10 +10366,10 @@
       <c r="B42" s="55">
         <v>2</v>
       </c>
-      <c r="C42" s="87" t="s">
+      <c r="C42" s="88" t="s">
         <v>151</v>
       </c>
-      <c r="D42" s="87"/>
+      <c r="D42" s="88"/>
       <c r="E42" s="54">
         <f t="shared" ref="E42:AK42" si="7">SUM(E43:E61)</f>
         <v>45</v>
@@ -11748,10 +11749,10 @@
     </row>
     <row r="62" spans="2:37" ht="19.5" customHeight="1">
       <c r="B62" s="55"/>
-      <c r="C62" s="87" t="s">
+      <c r="C62" s="88" t="s">
         <v>170</v>
       </c>
-      <c r="D62" s="87"/>
+      <c r="D62" s="88"/>
       <c r="E62" s="54">
         <f t="shared" ref="E62:W62" si="8">SUM(E63:E74)</f>
         <v>3</v>
@@ -12455,10 +12456,10 @@
     </row>
     <row r="75" spans="2:37" ht="19.5" customHeight="1">
       <c r="B75" s="55"/>
-      <c r="C75" s="87" t="s">
+      <c r="C75" s="88" t="s">
         <v>181</v>
       </c>
-      <c r="D75" s="87"/>
+      <c r="D75" s="88"/>
       <c r="E75" s="54"/>
       <c r="F75" s="54"/>
       <c r="G75" s="54"/>
@@ -12643,10 +12644,10 @@
     </row>
     <row r="79" spans="2:37" ht="19.5" customHeight="1">
       <c r="B79" s="55"/>
-      <c r="C79" s="87" t="s">
+      <c r="C79" s="88" t="s">
         <v>185</v>
       </c>
-      <c r="D79" s="87"/>
+      <c r="D79" s="88"/>
       <c r="E79" s="54"/>
       <c r="F79" s="54"/>
       <c r="G79" s="54"/>
@@ -12812,10 +12813,10 @@
     </row>
     <row r="82" spans="2:37" ht="23.25" customHeight="1">
       <c r="B82" s="55"/>
-      <c r="C82" s="87" t="s">
+      <c r="C82" s="88" t="s">
         <v>186</v>
       </c>
-      <c r="D82" s="87"/>
+      <c r="D82" s="88"/>
       <c r="E82" s="54">
         <f t="shared" ref="E82:X82" si="10">SUM(E83:E92)</f>
         <v>58</v>
@@ -13500,10 +13501,10 @@
       <c r="B93" s="55">
         <v>6</v>
       </c>
-      <c r="C93" s="92" t="s">
+      <c r="C93" s="95" t="s">
         <v>193</v>
       </c>
-      <c r="D93" s="92"/>
+      <c r="D93" s="95"/>
       <c r="E93" s="54"/>
       <c r="F93" s="54"/>
       <c r="G93" s="54"/>
@@ -13585,10 +13586,10 @@
     </row>
     <row r="95" spans="2:37" ht="19.5" customHeight="1">
       <c r="B95" s="55"/>
-      <c r="C95" s="87" t="s">
+      <c r="C95" s="88" t="s">
         <v>194</v>
       </c>
-      <c r="D95" s="87"/>
+      <c r="D95" s="88"/>
       <c r="E95" s="54">
         <f>SUM(E96:E101)</f>
         <v>4</v>
@@ -13903,10 +13904,10 @@
     </row>
     <row r="102" spans="2:37" ht="19.5" customHeight="1">
       <c r="B102" s="55"/>
-      <c r="C102" s="87" t="s">
+      <c r="C102" s="88" t="s">
         <v>199</v>
       </c>
-      <c r="D102" s="87"/>
+      <c r="D102" s="88"/>
       <c r="E102" s="54">
         <f t="shared" ref="E102:M102" si="11">SUM(E103:E118)</f>
         <v>10</v>
@@ -14742,10 +14743,10 @@
       <c r="B119" s="55">
         <v>4</v>
       </c>
-      <c r="C119" s="87" t="s">
+      <c r="C119" s="88" t="s">
         <v>209</v>
       </c>
-      <c r="D119" s="87"/>
+      <c r="D119" s="88"/>
       <c r="E119" s="54"/>
       <c r="F119" s="54"/>
       <c r="G119" s="54"/>
@@ -14874,10 +14875,10 @@
       <c r="B121" s="55">
         <v>1</v>
       </c>
-      <c r="C121" s="87" t="s">
+      <c r="C121" s="88" t="s">
         <v>210</v>
       </c>
-      <c r="D121" s="87"/>
+      <c r="D121" s="88"/>
       <c r="E121" s="54"/>
       <c r="F121" s="54"/>
       <c r="G121" s="54"/>
@@ -15376,10 +15377,10 @@
     </row>
     <row r="129" spans="2:37" ht="21" customHeight="1">
       <c r="B129" s="61"/>
-      <c r="C129" s="88" t="s">
+      <c r="C129" s="89" t="s">
         <v>218</v>
       </c>
-      <c r="D129" s="88"/>
+      <c r="D129" s="89"/>
       <c r="E129" s="60">
         <f t="shared" ref="E129:AJ129" si="14">+E130+E134+E137+E139+E144+E158+E162+E164+E167+E173+E179+E190+E193+E198+E202+E213+E215+E217+E220+E225</f>
         <v>54</v>
@@ -15515,10 +15516,10 @@
     </row>
     <row r="130" spans="2:37" ht="19.5" customHeight="1">
       <c r="B130" s="55"/>
-      <c r="C130" s="87" t="s">
+      <c r="C130" s="88" t="s">
         <v>219</v>
       </c>
-      <c r="D130" s="87"/>
+      <c r="D130" s="88"/>
       <c r="E130" s="54"/>
       <c r="F130" s="54"/>
       <c r="G130" s="54"/>
@@ -15748,10 +15749,10 @@
     </row>
     <row r="134" spans="2:37" ht="19.5" customHeight="1">
       <c r="B134" s="55"/>
-      <c r="C134" s="87" t="s">
+      <c r="C134" s="88" t="s">
         <v>223</v>
       </c>
-      <c r="D134" s="87"/>
+      <c r="D134" s="88"/>
       <c r="E134" s="54">
         <f t="shared" ref="E134:Q134" si="16">SUM(E135:E136)</f>
         <v>4</v>
@@ -15959,10 +15960,10 @@
     </row>
     <row r="137" spans="2:37" ht="19.5" customHeight="1">
       <c r="B137" s="55"/>
-      <c r="C137" s="87" t="s">
+      <c r="C137" s="88" t="s">
         <v>226</v>
       </c>
-      <c r="D137" s="87"/>
+      <c r="D137" s="88"/>
       <c r="E137" s="54"/>
       <c r="F137" s="54"/>
       <c r="G137" s="54"/>
@@ -16079,10 +16080,10 @@
     </row>
     <row r="139" spans="2:37" ht="19.5" customHeight="1">
       <c r="B139" s="55"/>
-      <c r="C139" s="87" t="s">
+      <c r="C139" s="88" t="s">
         <v>227</v>
       </c>
-      <c r="D139" s="87"/>
+      <c r="D139" s="88"/>
       <c r="E139" s="54"/>
       <c r="F139" s="54"/>
       <c r="G139" s="54"/>
@@ -16357,10 +16358,10 @@
       <c r="B144" s="55">
         <v>1</v>
       </c>
-      <c r="C144" s="87" t="s">
+      <c r="C144" s="88" t="s">
         <v>228</v>
       </c>
-      <c r="D144" s="87"/>
+      <c r="D144" s="88"/>
       <c r="E144" s="54">
         <f t="shared" ref="E144:AK144" si="19">SUM(E145:E157)</f>
         <v>12</v>
@@ -17230,10 +17231,10 @@
     </row>
     <row r="158" spans="2:37" ht="19.5" customHeight="1">
       <c r="B158" s="55"/>
-      <c r="C158" s="87" t="s">
+      <c r="C158" s="88" t="s">
         <v>242</v>
       </c>
-      <c r="D158" s="87"/>
+      <c r="D158" s="88"/>
       <c r="E158" s="54">
         <f t="shared" ref="E158:AK158" si="20">SUM(E159:E161)</f>
         <v>4</v>
@@ -17581,10 +17582,10 @@
     </row>
     <row r="162" spans="2:37" ht="19.5" customHeight="1">
       <c r="B162" s="55"/>
-      <c r="C162" s="87" t="s">
+      <c r="C162" s="88" t="s">
         <v>245</v>
       </c>
-      <c r="D162" s="87"/>
+      <c r="D162" s="88"/>
       <c r="E162" s="54">
         <f>SUM(E163)</f>
         <v>4</v>
@@ -17676,10 +17677,10 @@
     </row>
     <row r="164" spans="2:37" ht="19.5" customHeight="1">
       <c r="B164" s="55"/>
-      <c r="C164" s="87" t="s">
+      <c r="C164" s="88" t="s">
         <v>247</v>
       </c>
-      <c r="D164" s="87"/>
+      <c r="D164" s="88"/>
       <c r="E164" s="54">
         <f t="shared" ref="E164:K164" si="21">SUM(E165:E166)</f>
         <v>1</v>
@@ -17833,10 +17834,10 @@
     </row>
     <row r="167" spans="2:37" ht="19.5" customHeight="1">
       <c r="B167" s="55"/>
-      <c r="C167" s="87" t="s">
+      <c r="C167" s="88" t="s">
         <v>249</v>
       </c>
-      <c r="D167" s="87"/>
+      <c r="D167" s="88"/>
       <c r="E167" s="54">
         <f t="shared" ref="E167:K167" si="22">SUM(E168:E172)</f>
         <v>5</v>
@@ -18120,10 +18121,10 @@
     </row>
     <row r="173" spans="2:37" ht="19.5" customHeight="1">
       <c r="B173" s="55"/>
-      <c r="C173" s="87" t="s">
+      <c r="C173" s="88" t="s">
         <v>253</v>
       </c>
-      <c r="D173" s="87"/>
+      <c r="D173" s="88"/>
       <c r="E173" s="54">
         <f t="shared" ref="E173:J173" si="23">SUM(E174:E178)</f>
         <v>4</v>
@@ -18414,10 +18415,10 @@
     </row>
     <row r="179" spans="2:37" ht="19.5" customHeight="1">
       <c r="B179" s="55"/>
-      <c r="C179" s="87" t="s">
+      <c r="C179" s="88" t="s">
         <v>259</v>
       </c>
-      <c r="D179" s="87"/>
+      <c r="D179" s="88"/>
       <c r="E179" s="54">
         <f t="shared" ref="E179:X179" si="24">SUM(E180:E189)</f>
         <v>8</v>
@@ -19044,10 +19045,10 @@
     </row>
     <row r="190" spans="2:37" ht="19.5" customHeight="1">
       <c r="B190" s="55"/>
-      <c r="C190" s="87" t="s">
+      <c r="C190" s="88" t="s">
         <v>266</v>
       </c>
-      <c r="D190" s="87"/>
+      <c r="D190" s="88"/>
       <c r="E190" s="54"/>
       <c r="F190" s="54">
         <f>SUM(F191:F192)</f>
@@ -19183,10 +19184,10 @@
     </row>
     <row r="193" spans="2:37" ht="19.5" customHeight="1">
       <c r="B193" s="55"/>
-      <c r="C193" s="87" t="s">
+      <c r="C193" s="88" t="s">
         <v>267</v>
       </c>
-      <c r="D193" s="87"/>
+      <c r="D193" s="88"/>
       <c r="E193" s="54">
         <f>+E194+E195</f>
         <v>2</v>
@@ -19312,10 +19313,10 @@
       <c r="B196" s="55">
         <v>3</v>
       </c>
-      <c r="C196" s="87" t="s">
+      <c r="C196" s="88" t="s">
         <v>269</v>
       </c>
-      <c r="D196" s="87"/>
+      <c r="D196" s="88"/>
       <c r="E196" s="54"/>
       <c r="F196" s="54"/>
       <c r="G196" s="54"/>
@@ -19397,10 +19398,10 @@
     </row>
     <row r="198" spans="2:37" ht="19.5" customHeight="1">
       <c r="B198" s="55"/>
-      <c r="C198" s="87" t="s">
+      <c r="C198" s="88" t="s">
         <v>271</v>
       </c>
-      <c r="D198" s="87"/>
+      <c r="D198" s="88"/>
       <c r="E198" s="54">
         <f t="shared" ref="E198:J198" si="25">SUM(E199:E201)</f>
         <v>4</v>
@@ -19601,10 +19602,10 @@
       <c r="B202" s="55">
         <v>2</v>
       </c>
-      <c r="C202" s="87" t="s">
+      <c r="C202" s="88" t="s">
         <v>272</v>
       </c>
-      <c r="D202" s="87"/>
+      <c r="D202" s="88"/>
       <c r="E202" s="54"/>
       <c r="F202" s="54"/>
       <c r="G202" s="54"/>
@@ -20240,10 +20241,10 @@
     </row>
     <row r="213" spans="2:37" ht="19.5" customHeight="1">
       <c r="B213" s="55"/>
-      <c r="C213" s="87" t="s">
+      <c r="C213" s="88" t="s">
         <v>278</v>
       </c>
-      <c r="D213" s="87"/>
+      <c r="D213" s="88"/>
       <c r="E213" s="54"/>
       <c r="F213" s="54"/>
       <c r="G213" s="54"/>
@@ -20330,10 +20331,10 @@
     </row>
     <row r="215" spans="2:37" ht="19.5" customHeight="1">
       <c r="B215" s="55"/>
-      <c r="C215" s="87" t="s">
+      <c r="C215" s="88" t="s">
         <v>280</v>
       </c>
-      <c r="D215" s="87"/>
+      <c r="D215" s="88"/>
       <c r="E215" s="54"/>
       <c r="F215" s="54"/>
       <c r="G215" s="54"/>
@@ -20415,10 +20416,10 @@
     </row>
     <row r="217" spans="2:37" ht="19.5" customHeight="1">
       <c r="B217" s="55"/>
-      <c r="C217" s="87" t="s">
+      <c r="C217" s="88" t="s">
         <v>282</v>
       </c>
-      <c r="D217" s="87"/>
+      <c r="D217" s="88"/>
       <c r="E217" s="54"/>
       <c r="F217" s="54"/>
       <c r="G217" s="54">
@@ -20552,10 +20553,10 @@
     </row>
     <row r="220" spans="2:37" ht="19.5" customHeight="1">
       <c r="B220" s="55"/>
-      <c r="C220" s="87" t="s">
+      <c r="C220" s="88" t="s">
         <v>283</v>
       </c>
-      <c r="D220" s="87"/>
+      <c r="D220" s="88"/>
       <c r="E220" s="54">
         <f>SUM(E221:E224)</f>
         <v>4</v>
@@ -20784,10 +20785,10 @@
     </row>
     <row r="225" spans="2:37" ht="19.5" customHeight="1">
       <c r="B225" s="55"/>
-      <c r="C225" s="87" t="s">
+      <c r="C225" s="88" t="s">
         <v>286</v>
       </c>
-      <c r="D225" s="87"/>
+      <c r="D225" s="88"/>
       <c r="E225" s="54">
         <f>SUM(E226:E227)</f>
         <v>2</v>
@@ -20935,10 +20936,10 @@
     </row>
     <row r="228" spans="2:37" ht="21" customHeight="1">
       <c r="B228" s="61"/>
-      <c r="C228" s="88" t="s">
+      <c r="C228" s="89" t="s">
         <v>288</v>
       </c>
-      <c r="D228" s="88"/>
+      <c r="D228" s="89"/>
       <c r="E228" s="60">
         <f t="shared" ref="E228:AJ228" si="27">+E229+E231+E234+E237+E240+E242+E244+E247+E249+E251+E253+E255+E257+E268+E270+E275+E277+E279+E281+E289</f>
         <v>4</v>
@@ -21074,10 +21075,10 @@
     </row>
     <row r="229" spans="2:37" ht="19.5" customHeight="1">
       <c r="B229" s="55"/>
-      <c r="C229" s="87" t="s">
+      <c r="C229" s="88" t="s">
         <v>219</v>
       </c>
-      <c r="D229" s="87"/>
+      <c r="D229" s="88"/>
       <c r="E229" s="54"/>
       <c r="F229" s="54">
         <f>SUM(F230:F230)</f>
@@ -21174,10 +21175,10 @@
     </row>
     <row r="231" spans="2:37" ht="19.5" customHeight="1">
       <c r="B231" s="55"/>
-      <c r="C231" s="87" t="s">
+      <c r="C231" s="88" t="s">
         <v>226</v>
       </c>
-      <c r="D231" s="87"/>
+      <c r="D231" s="88"/>
       <c r="E231" s="54">
         <f>SUM(E232:E233)</f>
         <v>4</v>
@@ -21315,10 +21316,10 @@
     </row>
     <row r="234" spans="2:37" ht="19.5" customHeight="1">
       <c r="B234" s="55"/>
-      <c r="C234" s="87" t="s">
+      <c r="C234" s="88" t="s">
         <v>289</v>
       </c>
-      <c r="D234" s="87"/>
+      <c r="D234" s="88"/>
       <c r="E234" s="54"/>
       <c r="F234" s="54"/>
       <c r="G234" s="54"/>
@@ -21528,10 +21529,10 @@
     </row>
     <row r="237" spans="2:37" ht="19.5" customHeight="1">
       <c r="B237" s="55"/>
-      <c r="C237" s="87" t="s">
+      <c r="C237" s="88" t="s">
         <v>291</v>
       </c>
-      <c r="D237" s="87"/>
+      <c r="D237" s="88"/>
       <c r="E237" s="54"/>
       <c r="F237" s="54"/>
       <c r="G237" s="54"/>
@@ -21672,10 +21673,10 @@
     </row>
     <row r="240" spans="2:37" ht="19.5" customHeight="1">
       <c r="B240" s="55"/>
-      <c r="C240" s="87" t="s">
+      <c r="C240" s="88" t="s">
         <v>294</v>
       </c>
-      <c r="D240" s="87"/>
+      <c r="D240" s="88"/>
       <c r="E240" s="54"/>
       <c r="F240" s="54"/>
       <c r="G240" s="54">
@@ -21757,10 +21758,10 @@
     </row>
     <row r="242" spans="2:37" ht="19.5" customHeight="1">
       <c r="B242" s="55"/>
-      <c r="C242" s="87" t="s">
+      <c r="C242" s="88" t="s">
         <v>295</v>
       </c>
-      <c r="D242" s="87"/>
+      <c r="D242" s="88"/>
       <c r="E242" s="54"/>
       <c r="F242" s="54"/>
       <c r="G242" s="54"/>
@@ -21847,10 +21848,10 @@
     </row>
     <row r="244" spans="2:37" ht="19.5" customHeight="1">
       <c r="B244" s="55"/>
-      <c r="C244" s="87" t="s">
+      <c r="C244" s="88" t="s">
         <v>297</v>
       </c>
-      <c r="D244" s="87"/>
+      <c r="D244" s="88"/>
       <c r="E244" s="54"/>
       <c r="F244" s="54"/>
       <c r="G244" s="54"/>
@@ -21979,10 +21980,10 @@
     </row>
     <row r="247" spans="2:37" ht="19.5" customHeight="1">
       <c r="B247" s="55"/>
-      <c r="C247" s="87" t="s">
+      <c r="C247" s="88" t="s">
         <v>298</v>
       </c>
-      <c r="D247" s="87"/>
+      <c r="D247" s="88"/>
       <c r="E247" s="54"/>
       <c r="F247" s="54"/>
       <c r="G247" s="54">
@@ -22081,10 +22082,10 @@
       <c r="B249" s="55">
         <v>1</v>
       </c>
-      <c r="C249" s="87" t="s">
+      <c r="C249" s="88" t="s">
         <v>299</v>
       </c>
-      <c r="D249" s="87"/>
+      <c r="D249" s="88"/>
       <c r="E249" s="54"/>
       <c r="F249" s="54"/>
       <c r="G249" s="54"/>
@@ -22171,10 +22172,10 @@
     </row>
     <row r="251" spans="2:37" ht="19.5" customHeight="1">
       <c r="B251" s="55"/>
-      <c r="C251" s="87" t="s">
+      <c r="C251" s="88" t="s">
         <v>272</v>
       </c>
-      <c r="D251" s="87"/>
+      <c r="D251" s="88"/>
       <c r="E251" s="54"/>
       <c r="F251" s="54"/>
       <c r="G251" s="54"/>
@@ -22286,10 +22287,10 @@
     </row>
     <row r="253" spans="2:37" ht="19.5" customHeight="1">
       <c r="B253" s="55"/>
-      <c r="C253" s="87" t="s">
+      <c r="C253" s="88" t="s">
         <v>300</v>
       </c>
-      <c r="D253" s="87"/>
+      <c r="D253" s="88"/>
       <c r="E253" s="54"/>
       <c r="F253" s="54"/>
       <c r="G253" s="54"/>
@@ -22371,10 +22372,10 @@
     </row>
     <row r="255" spans="2:37" ht="19.5" customHeight="1">
       <c r="B255" s="55"/>
-      <c r="C255" s="87" t="s">
+      <c r="C255" s="88" t="s">
         <v>301</v>
       </c>
-      <c r="D255" s="87"/>
+      <c r="D255" s="88"/>
       <c r="E255" s="54"/>
       <c r="F255" s="54"/>
       <c r="G255" s="54">
@@ -22456,10 +22457,10 @@
     </row>
     <row r="257" spans="2:37" ht="19.5" customHeight="1">
       <c r="B257" s="55"/>
-      <c r="C257" s="87" t="s">
+      <c r="C257" s="88" t="s">
         <v>303</v>
       </c>
-      <c r="D257" s="87"/>
+      <c r="D257" s="88"/>
       <c r="E257" s="54"/>
       <c r="F257" s="54"/>
       <c r="G257" s="54">
@@ -22991,10 +22992,10 @@
     </row>
     <row r="268" spans="2:37" ht="19.5" customHeight="1">
       <c r="B268" s="55"/>
-      <c r="C268" s="87" t="s">
+      <c r="C268" s="88" t="s">
         <v>280</v>
       </c>
-      <c r="D268" s="87"/>
+      <c r="D268" s="88"/>
       <c r="E268" s="54"/>
       <c r="F268" s="54"/>
       <c r="G268" s="54"/>
@@ -23086,10 +23087,10 @@
     </row>
     <row r="270" spans="2:37" ht="19.5" customHeight="1">
       <c r="B270" s="55"/>
-      <c r="C270" s="87" t="s">
+      <c r="C270" s="88" t="s">
         <v>309</v>
       </c>
-      <c r="D270" s="87"/>
+      <c r="D270" s="88"/>
       <c r="E270" s="54"/>
       <c r="F270" s="54"/>
       <c r="G270" s="54"/>
@@ -23316,10 +23317,10 @@
     </row>
     <row r="275" spans="2:37" ht="19.5" customHeight="1">
       <c r="B275" s="55"/>
-      <c r="C275" s="87" t="s">
+      <c r="C275" s="88" t="s">
         <v>312</v>
       </c>
-      <c r="D275" s="87"/>
+      <c r="D275" s="88"/>
       <c r="E275" s="54"/>
       <c r="F275" s="54"/>
       <c r="G275" s="54">
@@ -23401,10 +23402,10 @@
     </row>
     <row r="277" spans="2:37" ht="19.5" customHeight="1">
       <c r="B277" s="55"/>
-      <c r="C277" s="87" t="s">
+      <c r="C277" s="88" t="s">
         <v>313</v>
       </c>
-      <c r="D277" s="87"/>
+      <c r="D277" s="88"/>
       <c r="E277" s="54"/>
       <c r="F277" s="54"/>
       <c r="G277" s="54"/>
@@ -23486,10 +23487,10 @@
     </row>
     <row r="279" spans="2:37" ht="19.5" customHeight="1">
       <c r="B279" s="55"/>
-      <c r="C279" s="87" t="s">
+      <c r="C279" s="88" t="s">
         <v>315</v>
       </c>
-      <c r="D279" s="87"/>
+      <c r="D279" s="88"/>
       <c r="E279" s="54"/>
       <c r="F279" s="54">
         <f>+F280</f>
@@ -23571,10 +23572,10 @@
     </row>
     <row r="281" spans="2:37" ht="19.5" customHeight="1">
       <c r="B281" s="55"/>
-      <c r="C281" s="87" t="s">
+      <c r="C281" s="88" t="s">
         <v>317</v>
       </c>
-      <c r="D281" s="87"/>
+      <c r="D281" s="88"/>
       <c r="E281" s="54"/>
       <c r="F281" s="54">
         <f>SUM(F282:F284)</f>
@@ -23752,10 +23753,10 @@
       <c r="B285" s="55">
         <v>1</v>
       </c>
-      <c r="C285" s="87" t="s">
+      <c r="C285" s="88" t="s">
         <v>319</v>
       </c>
-      <c r="D285" s="87"/>
+      <c r="D285" s="88"/>
       <c r="E285" s="54"/>
       <c r="F285" s="54"/>
       <c r="G285" s="54"/>
@@ -23839,10 +23840,10 @@
       <c r="B287" s="55">
         <v>2</v>
       </c>
-      <c r="C287" s="87" t="s">
+      <c r="C287" s="88" t="s">
         <v>320</v>
       </c>
-      <c r="D287" s="87"/>
+      <c r="D287" s="88"/>
       <c r="E287" s="54"/>
       <c r="F287" s="54"/>
       <c r="G287" s="54"/>
@@ -23924,10 +23925,10 @@
     </row>
     <row r="289" spans="2:37" ht="19.5" customHeight="1">
       <c r="B289" s="55"/>
-      <c r="C289" s="87" t="s">
+      <c r="C289" s="88" t="s">
         <v>322</v>
       </c>
-      <c r="D289" s="87"/>
+      <c r="D289" s="88"/>
       <c r="E289" s="54"/>
       <c r="F289" s="54">
         <f>+F290</f>
@@ -24014,10 +24015,10 @@
     </row>
     <row r="291" spans="2:37" ht="21" customHeight="1">
       <c r="B291" s="61"/>
-      <c r="C291" s="88" t="s">
+      <c r="C291" s="89" t="s">
         <v>323</v>
       </c>
-      <c r="D291" s="88"/>
+      <c r="D291" s="89"/>
       <c r="E291" s="60"/>
       <c r="F291" s="60">
         <f t="shared" ref="F291:AJ291" si="31">+F292+F294+F296+F299+F301+F304+F306+F309+F315+F331+F335+F337+F346+F348+F351+F362+F365+F367+F370+F372+F375+F379+F384+F386+F390+F396</f>
@@ -24150,10 +24151,10 @@
     </row>
     <row r="292" spans="2:37" ht="19.5" customHeight="1">
       <c r="B292" s="55"/>
-      <c r="C292" s="87" t="s">
+      <c r="C292" s="88" t="s">
         <v>324</v>
       </c>
-      <c r="D292" s="87"/>
+      <c r="D292" s="88"/>
       <c r="E292" s="54"/>
       <c r="F292" s="54"/>
       <c r="G292" s="54"/>
@@ -24245,10 +24246,10 @@
     </row>
     <row r="294" spans="2:37" ht="19.5" customHeight="1">
       <c r="B294" s="55"/>
-      <c r="C294" s="87" t="s">
+      <c r="C294" s="88" t="s">
         <v>326</v>
       </c>
-      <c r="D294" s="87"/>
+      <c r="D294" s="88"/>
       <c r="E294" s="54"/>
       <c r="F294" s="54"/>
       <c r="G294" s="54"/>
@@ -24330,10 +24331,10 @@
     </row>
     <row r="296" spans="2:37" ht="19.5" customHeight="1">
       <c r="B296" s="55"/>
-      <c r="C296" s="87" t="s">
+      <c r="C296" s="88" t="s">
         <v>328</v>
       </c>
-      <c r="D296" s="87"/>
+      <c r="D296" s="88"/>
       <c r="E296" s="54"/>
       <c r="F296" s="54"/>
       <c r="G296" s="54"/>
@@ -24484,10 +24485,10 @@
     </row>
     <row r="299" spans="2:37" ht="19.5" customHeight="1">
       <c r="B299" s="55"/>
-      <c r="C299" s="87" t="s">
+      <c r="C299" s="88" t="s">
         <v>331</v>
       </c>
-      <c r="D299" s="87"/>
+      <c r="D299" s="88"/>
       <c r="E299" s="54"/>
       <c r="F299" s="54"/>
       <c r="G299" s="54"/>
@@ -24569,10 +24570,10 @@
     </row>
     <row r="301" spans="2:37" ht="19.5" customHeight="1">
       <c r="B301" s="55"/>
-      <c r="C301" s="87" t="s">
+      <c r="C301" s="88" t="s">
         <v>333</v>
       </c>
-      <c r="D301" s="87"/>
+      <c r="D301" s="88"/>
       <c r="E301" s="54"/>
       <c r="F301" s="54"/>
       <c r="G301" s="54"/>
@@ -24731,10 +24732,10 @@
     </row>
     <row r="304" spans="2:37" ht="19.5" customHeight="1">
       <c r="B304" s="55"/>
-      <c r="C304" s="87" t="s">
+      <c r="C304" s="88" t="s">
         <v>336</v>
       </c>
-      <c r="D304" s="87"/>
+      <c r="D304" s="88"/>
       <c r="E304" s="54"/>
       <c r="F304" s="54"/>
       <c r="G304" s="54"/>
@@ -24826,10 +24827,10 @@
     </row>
     <row r="306" spans="2:37" ht="19.5" customHeight="1">
       <c r="B306" s="55"/>
-      <c r="C306" s="87" t="s">
+      <c r="C306" s="88" t="s">
         <v>338</v>
       </c>
-      <c r="D306" s="87"/>
+      <c r="D306" s="88"/>
       <c r="E306" s="54"/>
       <c r="F306" s="54"/>
       <c r="G306" s="54"/>
@@ -24968,10 +24969,10 @@
     </row>
     <row r="309" spans="2:37" ht="19.5" customHeight="1">
       <c r="B309" s="55"/>
-      <c r="C309" s="87" t="s">
+      <c r="C309" s="88" t="s">
         <v>341</v>
       </c>
-      <c r="D309" s="87"/>
+      <c r="D309" s="88"/>
       <c r="E309" s="54"/>
       <c r="F309" s="54"/>
       <c r="G309" s="54"/>
@@ -25264,10 +25265,10 @@
       <c r="B315" s="55">
         <v>1</v>
       </c>
-      <c r="C315" s="87" t="s">
+      <c r="C315" s="88" t="s">
         <v>346</v>
       </c>
-      <c r="D315" s="87"/>
+      <c r="D315" s="88"/>
       <c r="E315" s="54"/>
       <c r="F315" s="54"/>
       <c r="G315" s="54"/>
@@ -26182,10 +26183,10 @@
       <c r="B331" s="55">
         <v>2</v>
       </c>
-      <c r="C331" s="87" t="s">
+      <c r="C331" s="88" t="s">
         <v>359</v>
       </c>
-      <c r="D331" s="87"/>
+      <c r="D331" s="88"/>
       <c r="E331" s="54"/>
       <c r="F331" s="54"/>
       <c r="G331" s="54"/>
@@ -26481,10 +26482,10 @@
       <c r="B335" s="55">
         <v>4</v>
       </c>
-      <c r="C335" s="87" t="s">
+      <c r="C335" s="88" t="s">
         <v>362</v>
       </c>
-      <c r="D335" s="87"/>
+      <c r="D335" s="88"/>
       <c r="E335" s="54"/>
       <c r="F335" s="54"/>
       <c r="G335" s="54"/>
@@ -26658,10 +26659,10 @@
       <c r="B337" s="55">
         <v>6</v>
       </c>
-      <c r="C337" s="87" t="s">
+      <c r="C337" s="88" t="s">
         <v>364</v>
       </c>
-      <c r="D337" s="87"/>
+      <c r="D337" s="88"/>
       <c r="E337" s="54"/>
       <c r="F337" s="54">
         <f t="shared" ref="F337:AK337" si="40">SUM(F338:F345)</f>
@@ -27202,10 +27203,10 @@
     </row>
     <row r="346" spans="2:37" ht="19.5" customHeight="1">
       <c r="B346" s="55"/>
-      <c r="C346" s="87" t="s">
+      <c r="C346" s="88" t="s">
         <v>373</v>
       </c>
-      <c r="D346" s="87"/>
+      <c r="D346" s="88"/>
       <c r="E346" s="54"/>
       <c r="F346" s="54"/>
       <c r="G346" s="54"/>
@@ -27292,10 +27293,10 @@
     </row>
     <row r="348" spans="2:37" ht="19.5" customHeight="1">
       <c r="B348" s="55"/>
-      <c r="C348" s="87" t="s">
+      <c r="C348" s="88" t="s">
         <v>375</v>
       </c>
-      <c r="D348" s="87"/>
+      <c r="D348" s="88"/>
       <c r="E348" s="54"/>
       <c r="F348" s="54"/>
       <c r="G348" s="54"/>
@@ -27465,10 +27466,10 @@
       <c r="B351" s="55">
         <v>5</v>
       </c>
-      <c r="C351" s="87" t="s">
+      <c r="C351" s="88" t="s">
         <v>378</v>
       </c>
-      <c r="D351" s="87"/>
+      <c r="D351" s="88"/>
       <c r="E351" s="54"/>
       <c r="F351" s="54"/>
       <c r="G351" s="54"/>
@@ -28120,10 +28121,10 @@
     </row>
     <row r="362" spans="2:37" ht="19.5" customHeight="1">
       <c r="B362" s="55"/>
-      <c r="C362" s="87" t="s">
+      <c r="C362" s="88" t="s">
         <v>388</v>
       </c>
-      <c r="D362" s="87"/>
+      <c r="D362" s="88"/>
       <c r="E362" s="54"/>
       <c r="F362" s="54"/>
       <c r="G362" s="54"/>
@@ -28247,10 +28248,10 @@
     </row>
     <row r="365" spans="2:37" ht="19.5" customHeight="1">
       <c r="B365" s="55"/>
-      <c r="C365" s="87" t="s">
+      <c r="C365" s="88" t="s">
         <v>390</v>
       </c>
-      <c r="D365" s="87"/>
+      <c r="D365" s="88"/>
       <c r="E365" s="54"/>
       <c r="F365" s="54"/>
       <c r="G365" s="54"/>
@@ -28347,10 +28348,10 @@
     </row>
     <row r="367" spans="2:37" ht="19.5" customHeight="1">
       <c r="B367" s="55"/>
-      <c r="C367" s="87" t="s">
+      <c r="C367" s="88" t="s">
         <v>391</v>
       </c>
-      <c r="D367" s="87"/>
+      <c r="D367" s="88"/>
       <c r="E367" s="54"/>
       <c r="F367" s="54"/>
       <c r="G367" s="54"/>
@@ -28504,10 +28505,10 @@
     </row>
     <row r="370" spans="2:37" ht="19.5" customHeight="1">
       <c r="B370" s="55"/>
-      <c r="C370" s="87" t="s">
+      <c r="C370" s="88" t="s">
         <v>394</v>
       </c>
-      <c r="D370" s="87"/>
+      <c r="D370" s="88"/>
       <c r="E370" s="54"/>
       <c r="F370" s="54"/>
       <c r="G370" s="54"/>
@@ -28589,10 +28590,10 @@
     </row>
     <row r="372" spans="2:37" ht="19.5" customHeight="1">
       <c r="B372" s="55"/>
-      <c r="C372" s="87" t="s">
+      <c r="C372" s="88" t="s">
         <v>395</v>
       </c>
-      <c r="D372" s="87"/>
+      <c r="D372" s="88"/>
       <c r="E372" s="54"/>
       <c r="F372" s="54"/>
       <c r="G372" s="54"/>
@@ -28746,10 +28747,10 @@
       <c r="B375" s="55">
         <v>3</v>
       </c>
-      <c r="C375" s="87" t="s">
+      <c r="C375" s="88" t="s">
         <v>397</v>
       </c>
-      <c r="D375" s="87"/>
+      <c r="D375" s="88"/>
       <c r="E375" s="54"/>
       <c r="F375" s="54"/>
       <c r="G375" s="54"/>
@@ -28967,10 +28968,10 @@
     </row>
     <row r="379" spans="2:37" ht="19.5" customHeight="1">
       <c r="B379" s="55"/>
-      <c r="C379" s="87" t="s">
+      <c r="C379" s="88" t="s">
         <v>398</v>
       </c>
-      <c r="D379" s="87"/>
+      <c r="D379" s="88"/>
       <c r="E379" s="54"/>
       <c r="F379" s="54"/>
       <c r="G379" s="54"/>
@@ -29199,10 +29200,10 @@
     </row>
     <row r="384" spans="2:37" ht="19.5" customHeight="1">
       <c r="B384" s="55"/>
-      <c r="C384" s="87" t="s">
+      <c r="C384" s="88" t="s">
         <v>402</v>
       </c>
-      <c r="D384" s="87"/>
+      <c r="D384" s="88"/>
       <c r="E384" s="54"/>
       <c r="F384" s="54"/>
       <c r="G384" s="54"/>
@@ -29284,10 +29285,10 @@
     </row>
     <row r="386" spans="2:37" ht="19.5" customHeight="1">
       <c r="B386" s="55"/>
-      <c r="C386" s="87" t="s">
+      <c r="C386" s="88" t="s">
         <v>404</v>
       </c>
-      <c r="D386" s="87"/>
+      <c r="D386" s="88"/>
       <c r="E386" s="54"/>
       <c r="F386" s="54"/>
       <c r="G386" s="54"/>
@@ -29486,10 +29487,10 @@
     </row>
     <row r="390" spans="2:37" ht="19.5" customHeight="1">
       <c r="B390" s="55"/>
-      <c r="C390" s="87" t="s">
+      <c r="C390" s="88" t="s">
         <v>407</v>
       </c>
-      <c r="D390" s="87"/>
+      <c r="D390" s="88"/>
       <c r="E390" s="54"/>
       <c r="F390" s="54"/>
       <c r="G390" s="54"/>
@@ -29678,10 +29679,10 @@
       <c r="B394" s="55">
         <v>7</v>
       </c>
-      <c r="C394" s="87" t="s">
+      <c r="C394" s="88" t="s">
         <v>411</v>
       </c>
-      <c r="D394" s="87"/>
+      <c r="D394" s="88"/>
       <c r="E394" s="54"/>
       <c r="F394" s="54"/>
       <c r="G394" s="54"/>
@@ -29763,10 +29764,10 @@
     </row>
     <row r="396" spans="2:37" ht="19.5" customHeight="1">
       <c r="B396" s="55"/>
-      <c r="C396" s="87" t="s">
+      <c r="C396" s="88" t="s">
         <v>412</v>
       </c>
-      <c r="D396" s="87"/>
+      <c r="D396" s="88"/>
       <c r="E396" s="54"/>
       <c r="F396" s="54"/>
       <c r="G396" s="54"/>
@@ -30127,10 +30128,10 @@
     </row>
     <row r="403" spans="2:38" s="37" customFormat="1" ht="22.5" customHeight="1" thickTop="1" thickBot="1">
       <c r="B403" s="42"/>
-      <c r="C403" s="89" t="s">
+      <c r="C403" s="92" t="s">
         <v>419</v>
       </c>
-      <c r="D403" s="89"/>
+      <c r="D403" s="92"/>
       <c r="E403" s="40">
         <f t="shared" ref="E403:AK403" si="49">+E291+E228+E129+E8</f>
         <v>188</v>
@@ -30269,10 +30270,10 @@
       <c r="B404" s="35" t="s">
         <v>420</v>
       </c>
-      <c r="C404" s="102" t="s">
+      <c r="C404" s="91" t="s">
         <v>421</v>
       </c>
-      <c r="D404" s="102"/>
+      <c r="D404" s="91"/>
       <c r="AC404" s="36"/>
       <c r="AD404" s="36"/>
       <c r="AE404" s="36"/>
@@ -30286,28 +30287,28 @@
       <c r="B405" s="35" t="s">
         <v>422</v>
       </c>
-      <c r="C405" s="103" t="s">
+      <c r="C405" s="90" t="s">
         <v>423</v>
       </c>
-      <c r="D405" s="103"/>
+      <c r="D405" s="90"/>
     </row>
     <row r="406" spans="2:38" ht="13.5" customHeight="1">
       <c r="B406" s="35" t="s">
         <v>424</v>
       </c>
-      <c r="C406" s="103" t="s">
+      <c r="C406" s="90" t="s">
         <v>425</v>
       </c>
-      <c r="D406" s="103"/>
+      <c r="D406" s="90"/>
     </row>
     <row r="407" spans="2:38" ht="13.5" customHeight="1">
       <c r="B407" s="35" t="s">
         <v>426</v>
       </c>
-      <c r="C407" s="103" t="s">
+      <c r="C407" s="90" t="s">
         <v>427</v>
       </c>
-      <c r="D407" s="103"/>
+      <c r="D407" s="90"/>
     </row>
     <row r="408" spans="2:38" ht="13.5" customHeight="1">
       <c r="B408" s="34"/>
@@ -30342,7 +30343,6 @@
     <mergeCell ref="C137:D137"/>
     <mergeCell ref="C139:D139"/>
     <mergeCell ref="C144:D144"/>
-    <mergeCell ref="C229:D229"/>
     <mergeCell ref="C231:D231"/>
     <mergeCell ref="C237:D237"/>
     <mergeCell ref="C240:D240"/>
@@ -30357,6 +30357,7 @@
     <mergeCell ref="C193:D193"/>
     <mergeCell ref="C198:D198"/>
     <mergeCell ref="C196:D196"/>
+    <mergeCell ref="C220:D220"/>
     <mergeCell ref="C315:D315"/>
     <mergeCell ref="C331:D331"/>
     <mergeCell ref="C242:D242"/>
@@ -30395,7 +30396,6 @@
     <mergeCell ref="C370:D370"/>
     <mergeCell ref="C367:D367"/>
     <mergeCell ref="C365:D365"/>
-    <mergeCell ref="C220:D220"/>
     <mergeCell ref="C225:D225"/>
     <mergeCell ref="C228:D228"/>
     <mergeCell ref="C268:D268"/>
@@ -30411,6 +30411,7 @@
     <mergeCell ref="C301:D301"/>
     <mergeCell ref="C299:D299"/>
     <mergeCell ref="C234:D234"/>
+    <mergeCell ref="C229:D229"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.39370078740157483" right="0.39370078740157483" top="0.39370078740157483" bottom="0" header="0" footer="0"/>
@@ -30432,15 +30433,15 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A26:K40"/>
-  <sheetFormatPr defaultColWidth="10.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="10.88671875" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="24.42578125" customWidth="1"/>
-    <col min="2" max="2" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="24.44140625" customWidth="1"/>
+    <col min="2" max="2" width="7.44140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
-    <col min="4" max="10" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="10" width="7.44140625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="6.42578125" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="5.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="6.44140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="5.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="26" spans="1:11">
@@ -30758,97 +30759,97 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:P59"/>
-  <sheetFormatPr defaultColWidth="10.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="10.88671875" defaultRowHeight="14.4"/>
   <cols>
     <col min="3" max="3" width="17" customWidth="1"/>
-    <col min="4" max="4" width="13.42578125" customWidth="1"/>
+    <col min="4" max="4" width="13.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="15.95">
-      <c r="A1" s="101" t="s">
+    <row r="1" spans="1:15" ht="15.6">
+      <c r="A1" s="104" t="s">
         <v>441</v>
       </c>
-      <c r="B1" s="101"/>
-      <c r="C1" s="101"/>
-      <c r="D1" s="101"/>
-      <c r="E1" s="101"/>
-      <c r="F1" s="101"/>
-      <c r="G1" s="101"/>
+      <c r="B1" s="104"/>
+      <c r="C1" s="104"/>
+      <c r="D1" s="104"/>
+      <c r="E1" s="104"/>
+      <c r="F1" s="104"/>
+      <c r="G1" s="104"/>
       <c r="H1" s="9"/>
-      <c r="I1" s="98" t="s">
+      <c r="I1" s="101" t="s">
         <v>442</v>
       </c>
-      <c r="J1" s="98"/>
-      <c r="K1" s="98"/>
-      <c r="L1" s="98"/>
-      <c r="M1" s="98"/>
-      <c r="N1" s="98"/>
-      <c r="O1" s="98"/>
-    </row>
-    <row r="2" spans="1:15" ht="15.95">
-      <c r="A2" s="101"/>
-      <c r="B2" s="101"/>
-      <c r="C2" s="101"/>
-      <c r="D2" s="101"/>
-      <c r="E2" s="101"/>
-      <c r="F2" s="101"/>
-      <c r="G2" s="101"/>
+      <c r="J1" s="101"/>
+      <c r="K1" s="101"/>
+      <c r="L1" s="101"/>
+      <c r="M1" s="101"/>
+      <c r="N1" s="101"/>
+      <c r="O1" s="101"/>
+    </row>
+    <row r="2" spans="1:15" ht="15.6">
+      <c r="A2" s="104"/>
+      <c r="B2" s="104"/>
+      <c r="C2" s="104"/>
+      <c r="D2" s="104"/>
+      <c r="E2" s="104"/>
+      <c r="F2" s="104"/>
+      <c r="G2" s="104"/>
       <c r="H2" s="9"/>
-      <c r="I2" s="98"/>
-      <c r="J2" s="98"/>
-      <c r="K2" s="98"/>
-      <c r="L2" s="98"/>
-      <c r="M2" s="98"/>
-      <c r="N2" s="98"/>
-      <c r="O2" s="98"/>
+      <c r="I2" s="101"/>
+      <c r="J2" s="101"/>
+      <c r="K2" s="101"/>
+      <c r="L2" s="101"/>
+      <c r="M2" s="101"/>
+      <c r="N2" s="101"/>
+      <c r="O2" s="101"/>
     </row>
     <row r="3" spans="1:15">
-      <c r="A3" s="95" t="s">
+      <c r="A3" s="98" t="s">
         <v>443</v>
       </c>
-      <c r="B3" s="95"/>
-      <c r="C3" s="95"/>
-      <c r="D3" s="95"/>
-      <c r="E3" s="95"/>
-      <c r="F3" s="95"/>
-      <c r="G3" s="95"/>
+      <c r="B3" s="98"/>
+      <c r="C3" s="98"/>
+      <c r="D3" s="98"/>
+      <c r="E3" s="98"/>
+      <c r="F3" s="98"/>
+      <c r="G3" s="98"/>
       <c r="H3" s="10"/>
-      <c r="I3" s="95" t="s">
+      <c r="I3" s="98" t="s">
         <v>444</v>
       </c>
-      <c r="J3" s="95"/>
-      <c r="K3" s="95"/>
-      <c r="L3" s="95"/>
-      <c r="M3" s="95"/>
-      <c r="N3" s="95"/>
-      <c r="O3" s="95"/>
+      <c r="J3" s="98"/>
+      <c r="K3" s="98"/>
+      <c r="L3" s="98"/>
+      <c r="M3" s="98"/>
+      <c r="N3" s="98"/>
+      <c r="O3" s="98"/>
     </row>
     <row r="4" spans="1:15">
-      <c r="A4" s="95"/>
-      <c r="B4" s="95"/>
-      <c r="C4" s="95"/>
-      <c r="D4" s="95"/>
-      <c r="E4" s="95"/>
-      <c r="F4" s="95"/>
-      <c r="G4" s="95"/>
+      <c r="A4" s="98"/>
+      <c r="B4" s="98"/>
+      <c r="C4" s="98"/>
+      <c r="D4" s="98"/>
+      <c r="E4" s="98"/>
+      <c r="F4" s="98"/>
+      <c r="G4" s="98"/>
       <c r="H4" s="11"/>
-      <c r="I4" s="95"/>
-      <c r="J4" s="95"/>
-      <c r="K4" s="95"/>
-      <c r="L4" s="95"/>
-      <c r="M4" s="95"/>
-      <c r="N4" s="95"/>
-      <c r="O4" s="95"/>
-    </row>
-    <row r="5" spans="1:15" ht="45">
-      <c r="A5" s="97" t="s">
+      <c r="I4" s="98"/>
+      <c r="J4" s="98"/>
+      <c r="K4" s="98"/>
+      <c r="L4" s="98"/>
+      <c r="M4" s="98"/>
+      <c r="N4" s="98"/>
+      <c r="O4" s="98"/>
+    </row>
+    <row r="5" spans="1:15" ht="41.4">
+      <c r="A5" s="100" t="s">
         <v>445</v>
       </c>
-      <c r="B5" s="97"/>
-      <c r="C5" s="97" t="s">
+      <c r="B5" s="100"/>
+      <c r="C5" s="100" t="s">
         <v>446</v>
       </c>
-      <c r="D5" s="97" t="s">
+      <c r="D5" s="100" t="s">
         <v>447</v>
       </c>
       <c r="E5" s="12" t="s">
@@ -30860,23 +30861,23 @@
       <c r="G5" s="12" t="s">
         <v>450</v>
       </c>
-      <c r="I5" s="97" t="s">
+      <c r="I5" s="100" t="s">
         <v>445</v>
       </c>
-      <c r="J5" s="97"/>
-      <c r="K5" s="97" t="s">
+      <c r="J5" s="100"/>
+      <c r="K5" s="100" t="s">
         <v>451</v>
       </c>
-      <c r="L5" s="97"/>
-      <c r="M5" s="97"/>
-      <c r="N5" s="97"/>
-      <c r="O5" s="97"/>
-    </row>
-    <row r="6" spans="1:15" ht="32.1">
-      <c r="A6" s="97"/>
-      <c r="B6" s="97"/>
-      <c r="C6" s="97"/>
-      <c r="D6" s="97"/>
+      <c r="L5" s="100"/>
+      <c r="M5" s="100"/>
+      <c r="N5" s="100"/>
+      <c r="O5" s="100"/>
+    </row>
+    <row r="6" spans="1:15" ht="42.6">
+      <c r="A6" s="100"/>
+      <c r="B6" s="100"/>
+      <c r="C6" s="100"/>
+      <c r="D6" s="100"/>
       <c r="E6" s="12" t="s">
         <v>452</v>
       </c>
@@ -30886,12 +30887,12 @@
       <c r="G6" s="12" t="s">
         <v>454</v>
       </c>
-      <c r="I6" s="97"/>
-      <c r="J6" s="97"/>
-      <c r="K6" s="97" t="s">
+      <c r="I6" s="100"/>
+      <c r="J6" s="100"/>
+      <c r="K6" s="100" t="s">
         <v>455</v>
       </c>
-      <c r="L6" s="97" t="s">
+      <c r="L6" s="100" t="s">
         <v>456</v>
       </c>
       <c r="M6" s="12" t="s">
@@ -30904,7 +30905,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="7" spans="1:15" ht="30">
+    <row r="7" spans="1:15" ht="27.6">
       <c r="A7" s="19">
         <v>2016</v>
       </c>
@@ -30929,10 +30930,10 @@
         <f>SUM(G8:G19)*1000</f>
         <v>1169544759</v>
       </c>
-      <c r="I7" s="97"/>
-      <c r="J7" s="97"/>
-      <c r="K7" s="97"/>
-      <c r="L7" s="97"/>
+      <c r="I7" s="100"/>
+      <c r="J7" s="100"/>
+      <c r="K7" s="100"/>
+      <c r="L7" s="100"/>
       <c r="M7" s="12" t="s">
         <v>458</v>
       </c>
@@ -30944,10 +30945,10 @@
       </c>
     </row>
     <row r="8" spans="1:15">
-      <c r="A8" s="95" t="s">
+      <c r="A8" s="98" t="s">
         <v>461</v>
       </c>
-      <c r="B8" s="95"/>
+      <c r="B8" s="98"/>
       <c r="C8" s="13">
         <v>226</v>
       </c>
@@ -30989,10 +30990,10 @@
       </c>
     </row>
     <row r="9" spans="1:15">
-      <c r="A9" s="95" t="s">
+      <c r="A9" s="98" t="s">
         <v>462</v>
       </c>
-      <c r="B9" s="95"/>
+      <c r="B9" s="98"/>
       <c r="C9" s="13">
         <v>226</v>
       </c>
@@ -31008,10 +31009,10 @@
       <c r="G9" s="13">
         <v>92449.615000000005</v>
       </c>
-      <c r="I9" s="95" t="s">
+      <c r="I9" s="98" t="s">
         <v>461</v>
       </c>
-      <c r="J9" s="95"/>
+      <c r="J9" s="98"/>
       <c r="K9" s="13">
         <v>25</v>
       </c>
@@ -31029,10 +31030,10 @@
       </c>
     </row>
     <row r="10" spans="1:15">
-      <c r="A10" s="95" t="s">
+      <c r="A10" s="98" t="s">
         <v>463</v>
       </c>
-      <c r="B10" s="95"/>
+      <c r="B10" s="98"/>
       <c r="C10" s="13">
         <v>226</v>
       </c>
@@ -31048,10 +31049,10 @@
       <c r="G10" s="13">
         <v>97345.934999999998</v>
       </c>
-      <c r="I10" s="95" t="s">
+      <c r="I10" s="98" t="s">
         <v>462</v>
       </c>
-      <c r="J10" s="95"/>
+      <c r="J10" s="98"/>
       <c r="K10" s="13">
         <v>25</v>
       </c>
@@ -31069,10 +31070,10 @@
       </c>
     </row>
     <row r="11" spans="1:15">
-      <c r="A11" s="95" t="s">
+      <c r="A11" s="98" t="s">
         <v>464</v>
       </c>
-      <c r="B11" s="95"/>
+      <c r="B11" s="98"/>
       <c r="C11" s="13">
         <v>226</v>
       </c>
@@ -31088,10 +31089,10 @@
       <c r="G11" s="13">
         <v>96357.847999999998</v>
       </c>
-      <c r="I11" s="95" t="s">
+      <c r="I11" s="98" t="s">
         <v>463</v>
       </c>
-      <c r="J11" s="95"/>
+      <c r="J11" s="98"/>
       <c r="K11" s="13">
         <v>25</v>
       </c>
@@ -31109,10 +31110,10 @@
       </c>
     </row>
     <row r="12" spans="1:15">
-      <c r="A12" s="95" t="s">
+      <c r="A12" s="98" t="s">
         <v>465</v>
       </c>
-      <c r="B12" s="95"/>
+      <c r="B12" s="98"/>
       <c r="C12" s="13">
         <v>226</v>
       </c>
@@ -31128,10 +31129,10 @@
       <c r="G12" s="13">
         <v>99297.52</v>
       </c>
-      <c r="I12" s="95" t="s">
+      <c r="I12" s="98" t="s">
         <v>464</v>
       </c>
-      <c r="J12" s="95"/>
+      <c r="J12" s="98"/>
       <c r="K12" s="13">
         <v>25</v>
       </c>
@@ -31149,10 +31150,10 @@
       </c>
     </row>
     <row r="13" spans="1:15">
-      <c r="A13" s="95" t="s">
+      <c r="A13" s="98" t="s">
         <v>466</v>
       </c>
-      <c r="B13" s="95"/>
+      <c r="B13" s="98"/>
       <c r="C13" s="13">
         <v>226</v>
       </c>
@@ -31168,10 +31169,10 @@
       <c r="G13" s="13">
         <v>96849.358999999997</v>
       </c>
-      <c r="I13" s="95" t="s">
+      <c r="I13" s="98" t="s">
         <v>465</v>
       </c>
-      <c r="J13" s="95"/>
+      <c r="J13" s="98"/>
       <c r="K13" s="13">
         <v>25</v>
       </c>
@@ -31189,10 +31190,10 @@
       </c>
     </row>
     <row r="14" spans="1:15">
-      <c r="A14" s="95" t="s">
+      <c r="A14" s="98" t="s">
         <v>467</v>
       </c>
-      <c r="B14" s="95"/>
+      <c r="B14" s="98"/>
       <c r="C14" s="13">
         <v>226</v>
       </c>
@@ -31208,10 +31209,10 @@
       <c r="G14" s="13">
         <v>98806.009000000005</v>
       </c>
-      <c r="I14" s="95" t="s">
+      <c r="I14" s="98" t="s">
         <v>466</v>
       </c>
-      <c r="J14" s="95"/>
+      <c r="J14" s="98"/>
       <c r="K14" s="13">
         <v>25</v>
       </c>
@@ -31229,10 +31230,10 @@
       </c>
     </row>
     <row r="15" spans="1:15">
-      <c r="A15" s="95" t="s">
+      <c r="A15" s="98" t="s">
         <v>468</v>
       </c>
-      <c r="B15" s="95"/>
+      <c r="B15" s="98"/>
       <c r="C15" s="13">
         <v>226</v>
       </c>
@@ -31248,10 +31249,10 @@
       <c r="G15" s="13">
         <v>100273.31200000001</v>
       </c>
-      <c r="I15" s="95" t="s">
+      <c r="I15" s="98" t="s">
         <v>467</v>
       </c>
-      <c r="J15" s="95"/>
+      <c r="J15" s="98"/>
       <c r="K15" s="13">
         <v>25</v>
       </c>
@@ -31269,10 +31270,10 @@
       </c>
     </row>
     <row r="16" spans="1:15">
-      <c r="A16" s="95" t="s">
+      <c r="A16" s="98" t="s">
         <v>469</v>
       </c>
-      <c r="B16" s="95"/>
+      <c r="B16" s="98"/>
       <c r="C16" s="13">
         <v>226</v>
       </c>
@@ -31288,10 +31289,10 @@
       <c r="G16" s="13">
         <v>95873.567999999999</v>
       </c>
-      <c r="I16" s="95" t="s">
+      <c r="I16" s="98" t="s">
         <v>468</v>
       </c>
-      <c r="J16" s="95"/>
+      <c r="J16" s="98"/>
       <c r="K16" s="13">
         <v>25</v>
       </c>
@@ -31309,10 +31310,10 @@
       </c>
     </row>
     <row r="17" spans="1:16">
-      <c r="A17" s="95" t="s">
+      <c r="A17" s="98" t="s">
         <v>470</v>
       </c>
-      <c r="B17" s="95"/>
+      <c r="B17" s="98"/>
       <c r="C17" s="13">
         <v>226</v>
       </c>
@@ -31328,10 +31329,10 @@
       <c r="G17" s="13">
         <v>98806.008000000002</v>
       </c>
-      <c r="I17" s="95" t="s">
+      <c r="I17" s="98" t="s">
         <v>469</v>
       </c>
-      <c r="J17" s="95"/>
+      <c r="J17" s="98"/>
       <c r="K17" s="13">
         <v>25</v>
       </c>
@@ -31349,10 +31350,10 @@
       </c>
     </row>
     <row r="18" spans="1:16">
-      <c r="A18" s="95" t="s">
+      <c r="A18" s="98" t="s">
         <v>471</v>
       </c>
-      <c r="B18" s="95"/>
+      <c r="B18" s="98"/>
       <c r="C18" s="13">
         <v>226</v>
       </c>
@@ -31368,10 +31369,10 @@
       <c r="G18" s="13">
         <v>95873.567999999999</v>
       </c>
-      <c r="I18" s="95" t="s">
+      <c r="I18" s="98" t="s">
         <v>470</v>
       </c>
-      <c r="J18" s="95"/>
+      <c r="J18" s="98"/>
       <c r="K18" s="13">
         <v>25</v>
       </c>
@@ -31389,10 +31390,10 @@
       </c>
     </row>
     <row r="19" spans="1:16">
-      <c r="A19" s="95" t="s">
+      <c r="A19" s="98" t="s">
         <v>472</v>
       </c>
-      <c r="B19" s="95"/>
+      <c r="B19" s="98"/>
       <c r="C19" s="13">
         <v>226</v>
       </c>
@@ -31408,10 +31409,10 @@
       <c r="G19" s="13">
         <v>99781.801000000007</v>
       </c>
-      <c r="I19" s="95" t="s">
+      <c r="I19" s="98" t="s">
         <v>471</v>
       </c>
-      <c r="J19" s="95"/>
+      <c r="J19" s="98"/>
       <c r="K19" s="13">
         <v>25</v>
       </c>
@@ -31432,18 +31433,18 @@
       <c r="A20" s="14" t="s">
         <v>71</v>
       </c>
-      <c r="B20" s="96" t="s">
+      <c r="B20" s="99" t="s">
         <v>473</v>
       </c>
-      <c r="C20" s="96"/>
-      <c r="D20" s="96"/>
-      <c r="E20" s="96"/>
-      <c r="F20" s="96"/>
-      <c r="G20" s="96"/>
-      <c r="I20" s="95" t="s">
+      <c r="C20" s="99"/>
+      <c r="D20" s="99"/>
+      <c r="E20" s="99"/>
+      <c r="F20" s="99"/>
+      <c r="G20" s="99"/>
+      <c r="I20" s="98" t="s">
         <v>472</v>
       </c>
-      <c r="J20" s="95"/>
+      <c r="J20" s="98"/>
       <c r="K20" s="13">
         <v>25</v>
       </c>
@@ -31460,221 +31461,221 @@
         <v>7569.8</v>
       </c>
     </row>
-    <row r="21" spans="1:16" ht="17.100000000000001">
+    <row r="21" spans="1:16" ht="15">
       <c r="A21" s="15" t="s">
         <v>474</v>
       </c>
-      <c r="B21" s="96" t="s">
+      <c r="B21" s="99" t="s">
         <v>475</v>
       </c>
-      <c r="C21" s="96"/>
-      <c r="D21" s="96"/>
-      <c r="E21" s="96"/>
-      <c r="F21" s="96"/>
-      <c r="G21" s="96"/>
-      <c r="I21" s="100" t="s">
+      <c r="C21" s="99"/>
+      <c r="D21" s="99"/>
+      <c r="E21" s="99"/>
+      <c r="F21" s="99"/>
+      <c r="G21" s="99"/>
+      <c r="I21" s="103" t="s">
         <v>71</v>
       </c>
-      <c r="J21" s="96" t="s">
+      <c r="J21" s="99" t="s">
         <v>476</v>
       </c>
-      <c r="K21" s="96"/>
-      <c r="L21" s="96"/>
-      <c r="M21" s="96"/>
-      <c r="N21" s="96"/>
-      <c r="O21" s="96"/>
-    </row>
-    <row r="22" spans="1:16" ht="17.100000000000001">
+      <c r="K21" s="99"/>
+      <c r="L21" s="99"/>
+      <c r="M21" s="99"/>
+      <c r="N21" s="99"/>
+      <c r="O21" s="99"/>
+    </row>
+    <row r="22" spans="1:16" ht="15">
       <c r="A22" s="15" t="s">
         <v>477</v>
       </c>
-      <c r="B22" s="96" t="s">
+      <c r="B22" s="99" t="s">
         <v>478</v>
       </c>
-      <c r="C22" s="96"/>
-      <c r="D22" s="96"/>
-      <c r="E22" s="96"/>
-      <c r="F22" s="96"/>
-      <c r="G22" s="96"/>
-      <c r="I22" s="100"/>
-      <c r="J22" s="96" t="s">
+      <c r="C22" s="99"/>
+      <c r="D22" s="99"/>
+      <c r="E22" s="99"/>
+      <c r="F22" s="99"/>
+      <c r="G22" s="99"/>
+      <c r="I22" s="103"/>
+      <c r="J22" s="99" t="s">
         <v>479</v>
       </c>
-      <c r="K22" s="96"/>
-      <c r="L22" s="96"/>
-      <c r="M22" s="96"/>
-      <c r="N22" s="96"/>
-      <c r="O22" s="96"/>
-    </row>
-    <row r="23" spans="1:16" ht="17.100000000000001">
+      <c r="K22" s="99"/>
+      <c r="L22" s="99"/>
+      <c r="M22" s="99"/>
+      <c r="N22" s="99"/>
+      <c r="O22" s="99"/>
+    </row>
+    <row r="23" spans="1:16" ht="15">
       <c r="A23" s="15" t="s">
         <v>480</v>
       </c>
-      <c r="B23" s="96" t="s">
+      <c r="B23" s="99" t="s">
         <v>481</v>
       </c>
-      <c r="C23" s="96"/>
-      <c r="D23" s="96"/>
-      <c r="E23" s="96"/>
-      <c r="F23" s="96"/>
-      <c r="G23" s="96"/>
+      <c r="C23" s="99"/>
+      <c r="D23" s="99"/>
+      <c r="E23" s="99"/>
+      <c r="F23" s="99"/>
+      <c r="G23" s="99"/>
       <c r="I23" s="15" t="s">
         <v>474</v>
       </c>
-      <c r="J23" s="96" t="s">
+      <c r="J23" s="99" t="s">
         <v>475</v>
       </c>
-      <c r="K23" s="96"/>
-      <c r="L23" s="96"/>
-      <c r="M23" s="96"/>
-      <c r="N23" s="96"/>
-      <c r="O23" s="96"/>
-    </row>
-    <row r="24" spans="1:16" ht="17.100000000000001">
+      <c r="K23" s="99"/>
+      <c r="L23" s="99"/>
+      <c r="M23" s="99"/>
+      <c r="N23" s="99"/>
+      <c r="O23" s="99"/>
+    </row>
+    <row r="24" spans="1:16" ht="15">
       <c r="A24" s="15" t="s">
         <v>482</v>
       </c>
-      <c r="B24" s="96" t="s">
+      <c r="B24" s="99" t="s">
         <v>483</v>
       </c>
-      <c r="C24" s="96"/>
-      <c r="D24" s="96"/>
-      <c r="E24" s="96"/>
-      <c r="F24" s="96"/>
-      <c r="G24" s="96"/>
+      <c r="C24" s="99"/>
+      <c r="D24" s="99"/>
+      <c r="E24" s="99"/>
+      <c r="F24" s="99"/>
+      <c r="G24" s="99"/>
       <c r="I24" s="15" t="s">
         <v>477</v>
       </c>
-      <c r="J24" s="96" t="s">
+      <c r="J24" s="99" t="s">
         <v>484</v>
       </c>
-      <c r="K24" s="96"/>
-      <c r="L24" s="96"/>
-      <c r="M24" s="96"/>
-      <c r="N24" s="96"/>
-      <c r="O24" s="96"/>
-    </row>
-    <row r="25" spans="1:16" ht="17.100000000000001">
+      <c r="K24" s="99"/>
+      <c r="L24" s="99"/>
+      <c r="M24" s="99"/>
+      <c r="N24" s="99"/>
+      <c r="O24" s="99"/>
+    </row>
+    <row r="25" spans="1:16" ht="15">
       <c r="A25" s="15" t="s">
         <v>485</v>
       </c>
-      <c r="B25" s="96" t="s">
+      <c r="B25" s="99" t="s">
         <v>486</v>
       </c>
-      <c r="C25" s="96"/>
-      <c r="D25" s="96"/>
-      <c r="E25" s="96"/>
-      <c r="F25" s="96"/>
-      <c r="G25" s="96"/>
-      <c r="I25" s="93"/>
-      <c r="J25" s="93"/>
+      <c r="C25" s="99"/>
+      <c r="D25" s="99"/>
+      <c r="E25" s="99"/>
+      <c r="F25" s="99"/>
+      <c r="G25" s="99"/>
+      <c r="I25" s="96"/>
+      <c r="J25" s="96"/>
     </row>
     <row r="26" spans="1:16">
-      <c r="A26" s="94" t="s">
+      <c r="A26" s="97" t="s">
         <v>487</v>
       </c>
-      <c r="B26" s="94"/>
-      <c r="I26" s="94" t="s">
+      <c r="B26" s="97"/>
+      <c r="I26" s="97" t="s">
         <v>487</v>
       </c>
-      <c r="J26" s="94"/>
+      <c r="J26" s="97"/>
     </row>
     <row r="28" spans="1:16">
-      <c r="A28" s="98" t="s">
+      <c r="A28" s="101" t="s">
         <v>488</v>
       </c>
-      <c r="B28" s="98"/>
-      <c r="C28" s="98"/>
-      <c r="D28" s="98"/>
-      <c r="E28" s="98"/>
-      <c r="F28" s="98"/>
-      <c r="G28" s="98"/>
-      <c r="I28" s="98" t="s">
+      <c r="B28" s="101"/>
+      <c r="C28" s="101"/>
+      <c r="D28" s="101"/>
+      <c r="E28" s="101"/>
+      <c r="F28" s="101"/>
+      <c r="G28" s="101"/>
+      <c r="I28" s="101" t="s">
         <v>489</v>
       </c>
-      <c r="J28" s="98"/>
-      <c r="K28" s="98"/>
-      <c r="L28" s="98"/>
-      <c r="M28" s="98"/>
-      <c r="N28" s="98"/>
-      <c r="O28" s="98"/>
-      <c r="P28" s="98"/>
+      <c r="J28" s="101"/>
+      <c r="K28" s="101"/>
+      <c r="L28" s="101"/>
+      <c r="M28" s="101"/>
+      <c r="N28" s="101"/>
+      <c r="O28" s="101"/>
+      <c r="P28" s="101"/>
     </row>
     <row r="29" spans="1:16">
-      <c r="A29" s="98"/>
-      <c r="B29" s="98"/>
-      <c r="C29" s="98"/>
-      <c r="D29" s="98"/>
-      <c r="E29" s="98"/>
-      <c r="F29" s="98"/>
-      <c r="G29" s="98"/>
-      <c r="I29" s="98"/>
-      <c r="J29" s="98"/>
-      <c r="K29" s="98"/>
-      <c r="L29" s="98"/>
-      <c r="M29" s="98"/>
-      <c r="N29" s="98"/>
-      <c r="O29" s="98"/>
-      <c r="P29" s="98"/>
+      <c r="A29" s="101"/>
+      <c r="B29" s="101"/>
+      <c r="C29" s="101"/>
+      <c r="D29" s="101"/>
+      <c r="E29" s="101"/>
+      <c r="F29" s="101"/>
+      <c r="G29" s="101"/>
+      <c r="I29" s="101"/>
+      <c r="J29" s="101"/>
+      <c r="K29" s="101"/>
+      <c r="L29" s="101"/>
+      <c r="M29" s="101"/>
+      <c r="N29" s="101"/>
+      <c r="O29" s="101"/>
+      <c r="P29" s="101"/>
     </row>
     <row r="30" spans="1:16">
-      <c r="A30" s="99" t="s">
+      <c r="A30" s="102" t="s">
         <v>490</v>
       </c>
-      <c r="B30" s="99"/>
-      <c r="C30" s="99"/>
-      <c r="D30" s="99"/>
-      <c r="E30" s="99"/>
-      <c r="F30" s="99"/>
-      <c r="G30" s="99"/>
-      <c r="I30" s="99" t="s">
+      <c r="B30" s="102"/>
+      <c r="C30" s="102"/>
+      <c r="D30" s="102"/>
+      <c r="E30" s="102"/>
+      <c r="F30" s="102"/>
+      <c r="G30" s="102"/>
+      <c r="I30" s="102" t="s">
         <v>491</v>
       </c>
-      <c r="J30" s="99"/>
-      <c r="K30" s="99"/>
-      <c r="L30" s="99"/>
-      <c r="M30" s="99"/>
-      <c r="N30" s="99"/>
-      <c r="O30" s="99"/>
-      <c r="P30" s="99"/>
+      <c r="J30" s="102"/>
+      <c r="K30" s="102"/>
+      <c r="L30" s="102"/>
+      <c r="M30" s="102"/>
+      <c r="N30" s="102"/>
+      <c r="O30" s="102"/>
+      <c r="P30" s="102"/>
     </row>
     <row r="31" spans="1:16">
-      <c r="A31" s="93"/>
-      <c r="B31" s="93"/>
-      <c r="C31" s="93"/>
-      <c r="D31" s="93"/>
-      <c r="E31" s="93"/>
-      <c r="F31" s="93"/>
-      <c r="G31" s="93"/>
-      <c r="I31" s="93"/>
-      <c r="J31" s="93"/>
-      <c r="K31" s="93"/>
-      <c r="L31" s="93"/>
-      <c r="M31" s="93"/>
-      <c r="N31" s="93"/>
-      <c r="O31" s="93"/>
-      <c r="P31" s="93"/>
-    </row>
-    <row r="32" spans="1:16" ht="45">
-      <c r="A32" s="97" t="s">
+      <c r="A31" s="96"/>
+      <c r="B31" s="96"/>
+      <c r="C31" s="96"/>
+      <c r="D31" s="96"/>
+      <c r="E31" s="96"/>
+      <c r="F31" s="96"/>
+      <c r="G31" s="96"/>
+      <c r="I31" s="96"/>
+      <c r="J31" s="96"/>
+      <c r="K31" s="96"/>
+      <c r="L31" s="96"/>
+      <c r="M31" s="96"/>
+      <c r="N31" s="96"/>
+      <c r="O31" s="96"/>
+      <c r="P31" s="96"/>
+    </row>
+    <row r="32" spans="1:16" ht="41.4">
+      <c r="A32" s="100" t="s">
         <v>445</v>
       </c>
-      <c r="B32" s="97"/>
-      <c r="C32" s="97" t="s">
+      <c r="B32" s="100"/>
+      <c r="C32" s="100" t="s">
         <v>492</v>
       </c>
-      <c r="D32" s="97"/>
-      <c r="E32" s="97"/>
-      <c r="F32" s="97"/>
-      <c r="G32" s="97"/>
-      <c r="I32" s="97" t="s">
+      <c r="D32" s="100"/>
+      <c r="E32" s="100"/>
+      <c r="F32" s="100"/>
+      <c r="G32" s="100"/>
+      <c r="I32" s="100" t="s">
         <v>445</v>
       </c>
-      <c r="J32" s="97"/>
+      <c r="J32" s="100"/>
       <c r="K32" s="12" t="s">
         <v>493</v>
       </c>
-      <c r="L32" s="97" t="s">
+      <c r="L32" s="100" t="s">
         <v>494</v>
       </c>
       <c r="M32" s="12" t="s">
@@ -31690,13 +31691,13 @@
         <v>495</v>
       </c>
     </row>
-    <row r="33" spans="1:16" ht="32.1">
-      <c r="A33" s="97"/>
-      <c r="B33" s="97"/>
-      <c r="C33" s="97" t="s">
+    <row r="33" spans="1:16" ht="41.4">
+      <c r="A33" s="100"/>
+      <c r="B33" s="100"/>
+      <c r="C33" s="100" t="s">
         <v>455</v>
       </c>
-      <c r="D33" s="97" t="s">
+      <c r="D33" s="100" t="s">
         <v>456</v>
       </c>
       <c r="E33" s="12" t="s">
@@ -31708,12 +31709,12 @@
       <c r="G33" s="12" t="s">
         <v>457</v>
       </c>
-      <c r="I33" s="97"/>
-      <c r="J33" s="97"/>
+      <c r="I33" s="100"/>
+      <c r="J33" s="100"/>
       <c r="K33" s="12" t="s">
         <v>496</v>
       </c>
-      <c r="L33" s="97"/>
+      <c r="L33" s="100"/>
       <c r="M33" s="12" t="s">
         <v>497</v>
       </c>
@@ -31727,11 +31728,11 @@
         <v>498</v>
       </c>
     </row>
-    <row r="34" spans="1:16" ht="30">
-      <c r="A34" s="97"/>
-      <c r="B34" s="97"/>
-      <c r="C34" s="97"/>
-      <c r="D34" s="97"/>
+    <row r="34" spans="1:16" ht="27.6">
+      <c r="A34" s="100"/>
+      <c r="B34" s="100"/>
+      <c r="C34" s="100"/>
+      <c r="D34" s="100"/>
       <c r="E34" s="12" t="s">
         <v>497</v>
       </c>
@@ -31795,10 +31796,10 @@
         <f>SUM(G36:G47)*1000</f>
         <v>475509660.99999994</v>
       </c>
-      <c r="I35" s="95" t="s">
+      <c r="I35" s="98" t="s">
         <v>461</v>
       </c>
-      <c r="J35" s="95"/>
+      <c r="J35" s="98"/>
       <c r="K35" s="13">
         <v>32</v>
       </c>
@@ -31819,10 +31820,10 @@
       </c>
     </row>
     <row r="36" spans="1:16">
-      <c r="A36" s="95" t="s">
+      <c r="A36" s="98" t="s">
         <v>461</v>
       </c>
-      <c r="B36" s="95"/>
+      <c r="B36" s="98"/>
       <c r="C36" s="13">
         <v>48</v>
       </c>
@@ -31838,10 +31839,10 @@
       <c r="G36" s="13">
         <v>36978.737000000001</v>
       </c>
-      <c r="I36" s="95" t="s">
+      <c r="I36" s="98" t="s">
         <v>462</v>
       </c>
-      <c r="J36" s="95"/>
+      <c r="J36" s="98"/>
       <c r="K36" s="13">
         <v>32</v>
       </c>
@@ -31862,10 +31863,10 @@
       </c>
     </row>
     <row r="37" spans="1:16">
-      <c r="A37" s="95" t="s">
+      <c r="A37" s="98" t="s">
         <v>462</v>
       </c>
-      <c r="B37" s="95"/>
+      <c r="B37" s="98"/>
       <c r="C37" s="13">
         <v>48</v>
       </c>
@@ -31881,10 +31882,10 @@
       <c r="G37" s="13">
         <v>37239.540999999997</v>
       </c>
-      <c r="I37" s="95" t="s">
+      <c r="I37" s="98" t="s">
         <v>463</v>
       </c>
-      <c r="J37" s="95"/>
+      <c r="J37" s="98"/>
       <c r="K37" s="13">
         <v>32</v>
       </c>
@@ -31905,10 +31906,10 @@
       </c>
     </row>
     <row r="38" spans="1:16">
-      <c r="A38" s="95" t="s">
+      <c r="A38" s="98" t="s">
         <v>463</v>
       </c>
-      <c r="B38" s="95"/>
+      <c r="B38" s="98"/>
       <c r="C38" s="13">
         <v>48</v>
       </c>
@@ -31924,10 +31925,10 @@
       <c r="G38" s="13">
         <v>36746.699999999997</v>
       </c>
-      <c r="I38" s="95" t="s">
+      <c r="I38" s="98" t="s">
         <v>464</v>
       </c>
-      <c r="J38" s="95"/>
+      <c r="J38" s="98"/>
       <c r="K38" s="13">
         <v>32</v>
       </c>
@@ -31948,10 +31949,10 @@
       </c>
     </row>
     <row r="39" spans="1:16">
-      <c r="A39" s="95" t="s">
+      <c r="A39" s="98" t="s">
         <v>464</v>
       </c>
-      <c r="B39" s="95"/>
+      <c r="B39" s="98"/>
       <c r="C39" s="13">
         <v>48</v>
       </c>
@@ -31967,10 +31968,10 @@
       <c r="G39" s="13">
         <v>38619.072</v>
       </c>
-      <c r="I39" s="95" t="s">
+      <c r="I39" s="98" t="s">
         <v>465</v>
       </c>
-      <c r="J39" s="95"/>
+      <c r="J39" s="98"/>
       <c r="K39" s="13">
         <v>32</v>
       </c>
@@ -31991,10 +31992,10 @@
       </c>
     </row>
     <row r="40" spans="1:16">
-      <c r="A40" s="95" t="s">
+      <c r="A40" s="98" t="s">
         <v>465</v>
       </c>
-      <c r="B40" s="95"/>
+      <c r="B40" s="98"/>
       <c r="C40" s="13">
         <v>48</v>
       </c>
@@ -32010,10 +32011,10 @@
       <c r="G40" s="13">
         <v>39357.822999999997</v>
       </c>
-      <c r="I40" s="95" t="s">
+      <c r="I40" s="98" t="s">
         <v>466</v>
       </c>
-      <c r="J40" s="95"/>
+      <c r="J40" s="98"/>
       <c r="K40" s="13">
         <v>32</v>
       </c>
@@ -32034,10 +32035,10 @@
       </c>
     </row>
     <row r="41" spans="1:16">
-      <c r="A41" s="95" t="s">
+      <c r="A41" s="98" t="s">
         <v>466</v>
       </c>
-      <c r="B41" s="95"/>
+      <c r="B41" s="98"/>
       <c r="C41" s="13">
         <v>48</v>
       </c>
@@ -32053,10 +32054,10 @@
       <c r="G41" s="13">
         <v>37431.334000000003</v>
       </c>
-      <c r="I41" s="95" t="s">
+      <c r="I41" s="98" t="s">
         <v>467</v>
       </c>
-      <c r="J41" s="95"/>
+      <c r="J41" s="98"/>
       <c r="K41" s="13">
         <v>32</v>
       </c>
@@ -32077,10 +32078,10 @@
       </c>
     </row>
     <row r="42" spans="1:16">
-      <c r="A42" s="95" t="s">
+      <c r="A42" s="98" t="s">
         <v>467</v>
       </c>
-      <c r="B42" s="95"/>
+      <c r="B42" s="98"/>
       <c r="C42" s="13">
         <v>48</v>
       </c>
@@ -32096,10 +32097,10 @@
       <c r="G42" s="13">
         <v>37326.470999999998</v>
       </c>
-      <c r="I42" s="95" t="s">
+      <c r="I42" s="98" t="s">
         <v>468</v>
       </c>
-      <c r="J42" s="95"/>
+      <c r="J42" s="98"/>
       <c r="K42" s="13">
         <v>32</v>
       </c>
@@ -32120,10 +32121,10 @@
       </c>
     </row>
     <row r="43" spans="1:16">
-      <c r="A43" s="95" t="s">
+      <c r="A43" s="98" t="s">
         <v>468</v>
       </c>
-      <c r="B43" s="95"/>
+      <c r="B43" s="98"/>
       <c r="C43" s="13">
         <v>48</v>
       </c>
@@ -32139,10 +32140,10 @@
       <c r="G43" s="13">
         <v>40265.175999999999</v>
       </c>
-      <c r="I43" s="95" t="s">
+      <c r="I43" s="98" t="s">
         <v>469</v>
       </c>
-      <c r="J43" s="95"/>
+      <c r="J43" s="98"/>
       <c r="K43" s="13">
         <v>32</v>
       </c>
@@ -32163,10 +32164,10 @@
       </c>
     </row>
     <row r="44" spans="1:16">
-      <c r="A44" s="95" t="s">
+      <c r="A44" s="98" t="s">
         <v>469</v>
       </c>
-      <c r="B44" s="95"/>
+      <c r="B44" s="98"/>
       <c r="C44" s="13">
         <v>48</v>
       </c>
@@ -32182,10 +32183,10 @@
       <c r="G44" s="13">
         <v>39636.254000000001</v>
       </c>
-      <c r="I44" s="95" t="s">
+      <c r="I44" s="98" t="s">
         <v>470</v>
       </c>
-      <c r="J44" s="95"/>
+      <c r="J44" s="98"/>
       <c r="K44" s="13">
         <v>32</v>
       </c>
@@ -32206,10 +32207,10 @@
       </c>
     </row>
     <row r="45" spans="1:16">
-      <c r="A45" s="95" t="s">
+      <c r="A45" s="98" t="s">
         <v>470</v>
       </c>
-      <c r="B45" s="95"/>
+      <c r="B45" s="98"/>
       <c r="C45" s="13">
         <v>48</v>
       </c>
@@ -32225,10 +32226,10 @@
       <c r="G45" s="13">
         <v>42836.974999999999</v>
       </c>
-      <c r="I45" s="95" t="s">
+      <c r="I45" s="98" t="s">
         <v>471</v>
       </c>
-      <c r="J45" s="95"/>
+      <c r="J45" s="98"/>
       <c r="K45" s="13">
         <v>32</v>
       </c>
@@ -32249,10 +32250,10 @@
       </c>
     </row>
     <row r="46" spans="1:16">
-      <c r="A46" s="95" t="s">
+      <c r="A46" s="98" t="s">
         <v>471</v>
       </c>
-      <c r="B46" s="95"/>
+      <c r="B46" s="98"/>
       <c r="C46" s="13">
         <v>48</v>
       </c>
@@ -32268,10 +32269,10 @@
       <c r="G46" s="13">
         <v>44749.88</v>
       </c>
-      <c r="I46" s="95" t="s">
+      <c r="I46" s="98" t="s">
         <v>472</v>
       </c>
-      <c r="J46" s="95"/>
+      <c r="J46" s="98"/>
       <c r="K46" s="13">
         <v>32</v>
       </c>
@@ -32291,11 +32292,11 @@
         <v>3378.7449999999999</v>
       </c>
     </row>
-    <row r="47" spans="1:16" ht="17.100000000000001">
-      <c r="A47" s="95" t="s">
+    <row r="47" spans="1:16" ht="15">
+      <c r="A47" s="98" t="s">
         <v>472</v>
       </c>
-      <c r="B47" s="95"/>
+      <c r="B47" s="98"/>
       <c r="C47" s="13">
         <v>48</v>
       </c>
@@ -32314,69 +32315,69 @@
       <c r="I47" s="15" t="s">
         <v>474</v>
       </c>
-      <c r="J47" s="96" t="s">
+      <c r="J47" s="99" t="s">
         <v>475</v>
       </c>
-      <c r="K47" s="96"/>
-      <c r="L47" s="96"/>
-      <c r="M47" s="96"/>
-      <c r="N47" s="96"/>
-      <c r="O47" s="96"/>
-      <c r="P47" s="96"/>
-    </row>
-    <row r="48" spans="1:16" ht="17.100000000000001">
+      <c r="K47" s="99"/>
+      <c r="L47" s="99"/>
+      <c r="M47" s="99"/>
+      <c r="N47" s="99"/>
+      <c r="O47" s="99"/>
+      <c r="P47" s="99"/>
+    </row>
+    <row r="48" spans="1:16" ht="15">
       <c r="A48" s="15" t="s">
         <v>474</v>
       </c>
-      <c r="B48" s="96" t="s">
+      <c r="B48" s="99" t="s">
         <v>475</v>
       </c>
-      <c r="C48" s="96"/>
-      <c r="D48" s="96"/>
-      <c r="E48" s="96"/>
-      <c r="F48" s="96"/>
-      <c r="G48" s="96"/>
+      <c r="C48" s="99"/>
+      <c r="D48" s="99"/>
+      <c r="E48" s="99"/>
+      <c r="F48" s="99"/>
+      <c r="G48" s="99"/>
       <c r="I48" s="15" t="s">
         <v>477</v>
       </c>
-      <c r="J48" s="96" t="s">
+      <c r="J48" s="99" t="s">
         <v>499</v>
       </c>
-      <c r="K48" s="96"/>
-      <c r="L48" s="96"/>
-      <c r="M48" s="96"/>
-      <c r="N48" s="96"/>
-      <c r="O48" s="96"/>
-      <c r="P48" s="96"/>
-    </row>
-    <row r="49" spans="1:10" ht="17.100000000000001">
+      <c r="K48" s="99"/>
+      <c r="L48" s="99"/>
+      <c r="M48" s="99"/>
+      <c r="N48" s="99"/>
+      <c r="O48" s="99"/>
+      <c r="P48" s="99"/>
+    </row>
+    <row r="49" spans="1:10" ht="15">
       <c r="A49" s="15" t="s">
         <v>477</v>
       </c>
-      <c r="B49" s="96" t="s">
+      <c r="B49" s="99" t="s">
         <v>484</v>
       </c>
-      <c r="C49" s="96"/>
-      <c r="D49" s="96"/>
-      <c r="E49" s="96"/>
-      <c r="F49" s="96"/>
-      <c r="G49" s="96"/>
-      <c r="I49" s="93"/>
-      <c r="J49" s="93"/>
+      <c r="C49" s="99"/>
+      <c r="D49" s="99"/>
+      <c r="E49" s="99"/>
+      <c r="F49" s="99"/>
+      <c r="G49" s="99"/>
+      <c r="I49" s="96"/>
+      <c r="J49" s="96"/>
     </row>
     <row r="50" spans="1:10" ht="37.5" customHeight="1">
-      <c r="A50" s="93"/>
-      <c r="B50" s="93"/>
-      <c r="I50" s="94" t="s">
+      <c r="A50" s="96"/>
+      <c r="B50" s="96"/>
+      <c r="I50" s="97" t="s">
         <v>487</v>
       </c>
-      <c r="J50" s="94"/>
+      <c r="J50" s="97"/>
     </row>
     <row r="51" spans="1:10" ht="33" customHeight="1">
-      <c r="A51" s="94" t="s">
+      <c r="A51" s="97" t="s">
         <v>487</v>
       </c>
-      <c r="B51" s="94"/>
+      <c r="B51" s="97"/>
     </row>
     <row r="54" spans="1:10" ht="33.75" customHeight="1">
       <c r="C54" s="16" t="s">
@@ -32534,7 +32535,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A2:R338"/>
-  <sheetFormatPr defaultColWidth="10.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="10.88671875" defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="22" bestFit="1" customWidth="1"/>
   </cols>
@@ -32584,7 +32585,7 @@
         <v>382.92</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="15.95">
+    <row r="13" spans="1:3" ht="15.6">
       <c r="A13" s="27" t="s">
         <v>512</v>
       </c>
@@ -32599,7 +32600,7 @@
         <v>514</v>
       </c>
     </row>
-    <row r="17" spans="1:18" ht="306">
+    <row r="17" spans="1:18" ht="303.60000000000002">
       <c r="A17" s="30" t="s">
         <v>515</v>
       </c>
@@ -49344,486 +49345,486 @@
       </c>
     </row>
     <row r="317" spans="1:18">
-      <c r="A317" s="104" t="s">
+      <c r="A317" s="105" t="s">
         <v>70</v>
       </c>
-      <c r="B317" s="104"/>
-      <c r="C317" s="104"/>
-      <c r="D317" s="104"/>
-      <c r="E317" s="104"/>
-      <c r="F317" s="104"/>
-      <c r="G317" s="104"/>
-      <c r="H317" s="104"/>
-      <c r="I317" s="104"/>
-      <c r="J317" s="104"/>
-      <c r="K317" s="104"/>
-      <c r="L317" s="104"/>
-      <c r="M317" s="104"/>
-      <c r="N317" s="104"/>
-      <c r="O317" s="104"/>
-      <c r="P317" s="104"/>
-      <c r="Q317" s="104"/>
-      <c r="R317" s="104"/>
+      <c r="B317" s="105"/>
+      <c r="C317" s="105"/>
+      <c r="D317" s="105"/>
+      <c r="E317" s="105"/>
+      <c r="F317" s="105"/>
+      <c r="G317" s="105"/>
+      <c r="H317" s="105"/>
+      <c r="I317" s="105"/>
+      <c r="J317" s="105"/>
+      <c r="K317" s="105"/>
+      <c r="L317" s="105"/>
+      <c r="M317" s="105"/>
+      <c r="N317" s="105"/>
+      <c r="O317" s="105"/>
+      <c r="P317" s="105"/>
+      <c r="Q317" s="105"/>
+      <c r="R317" s="105"/>
     </row>
     <row r="318" spans="1:18">
-      <c r="A318" s="104" t="s">
+      <c r="A318" s="105" t="s">
         <v>832</v>
       </c>
-      <c r="B318" s="104"/>
-      <c r="C318" s="104"/>
-      <c r="D318" s="104"/>
-      <c r="E318" s="104"/>
-      <c r="F318" s="104"/>
-      <c r="G318" s="104"/>
-      <c r="H318" s="104"/>
-      <c r="I318" s="104"/>
-      <c r="J318" s="104"/>
-      <c r="K318" s="104"/>
-      <c r="L318" s="104"/>
-      <c r="M318" s="104"/>
-      <c r="N318" s="104"/>
-      <c r="O318" s="104"/>
-      <c r="P318" s="104"/>
-      <c r="Q318" s="104"/>
-      <c r="R318" s="104"/>
+      <c r="B318" s="105"/>
+      <c r="C318" s="105"/>
+      <c r="D318" s="105"/>
+      <c r="E318" s="105"/>
+      <c r="F318" s="105"/>
+      <c r="G318" s="105"/>
+      <c r="H318" s="105"/>
+      <c r="I318" s="105"/>
+      <c r="J318" s="105"/>
+      <c r="K318" s="105"/>
+      <c r="L318" s="105"/>
+      <c r="M318" s="105"/>
+      <c r="N318" s="105"/>
+      <c r="O318" s="105"/>
+      <c r="P318" s="105"/>
+      <c r="Q318" s="105"/>
+      <c r="R318" s="105"/>
     </row>
     <row r="319" spans="1:18">
-      <c r="A319" s="104" t="s">
+      <c r="A319" s="105" t="s">
         <v>833</v>
       </c>
-      <c r="B319" s="104"/>
-      <c r="C319" s="104"/>
-      <c r="D319" s="104"/>
-      <c r="E319" s="104"/>
-      <c r="F319" s="104"/>
-      <c r="G319" s="104"/>
-      <c r="H319" s="104"/>
-      <c r="I319" s="104"/>
-      <c r="J319" s="104"/>
-      <c r="K319" s="104"/>
-      <c r="L319" s="104"/>
-      <c r="M319" s="104"/>
-      <c r="N319" s="104"/>
-      <c r="O319" s="104"/>
-      <c r="P319" s="104"/>
-      <c r="Q319" s="104"/>
-      <c r="R319" s="104"/>
+      <c r="B319" s="105"/>
+      <c r="C319" s="105"/>
+      <c r="D319" s="105"/>
+      <c r="E319" s="105"/>
+      <c r="F319" s="105"/>
+      <c r="G319" s="105"/>
+      <c r="H319" s="105"/>
+      <c r="I319" s="105"/>
+      <c r="J319" s="105"/>
+      <c r="K319" s="105"/>
+      <c r="L319" s="105"/>
+      <c r="M319" s="105"/>
+      <c r="N319" s="105"/>
+      <c r="O319" s="105"/>
+      <c r="P319" s="105"/>
+      <c r="Q319" s="105"/>
+      <c r="R319" s="105"/>
     </row>
     <row r="320" spans="1:18">
-      <c r="A320" s="104" t="s">
+      <c r="A320" s="105" t="s">
         <v>834</v>
       </c>
-      <c r="B320" s="104"/>
-      <c r="C320" s="104"/>
-      <c r="D320" s="104"/>
-      <c r="E320" s="104"/>
-      <c r="F320" s="104"/>
-      <c r="G320" s="104"/>
-      <c r="H320" s="104"/>
-      <c r="I320" s="104"/>
-      <c r="J320" s="104"/>
-      <c r="K320" s="104"/>
-      <c r="L320" s="104"/>
-      <c r="M320" s="104"/>
-      <c r="N320" s="104"/>
-      <c r="O320" s="104"/>
-      <c r="P320" s="104"/>
-      <c r="Q320" s="104"/>
-      <c r="R320" s="104"/>
+      <c r="B320" s="105"/>
+      <c r="C320" s="105"/>
+      <c r="D320" s="105"/>
+      <c r="E320" s="105"/>
+      <c r="F320" s="105"/>
+      <c r="G320" s="105"/>
+      <c r="H320" s="105"/>
+      <c r="I320" s="105"/>
+      <c r="J320" s="105"/>
+      <c r="K320" s="105"/>
+      <c r="L320" s="105"/>
+      <c r="M320" s="105"/>
+      <c r="N320" s="105"/>
+      <c r="O320" s="105"/>
+      <c r="P320" s="105"/>
+      <c r="Q320" s="105"/>
+      <c r="R320" s="105"/>
     </row>
     <row r="321" spans="1:18">
-      <c r="A321" s="104" t="s">
+      <c r="A321" s="105" t="s">
         <v>835</v>
       </c>
-      <c r="B321" s="104"/>
-      <c r="C321" s="104"/>
-      <c r="D321" s="104"/>
-      <c r="E321" s="104"/>
-      <c r="F321" s="104"/>
-      <c r="G321" s="104"/>
-      <c r="H321" s="104"/>
-      <c r="I321" s="104"/>
-      <c r="J321" s="104"/>
-      <c r="K321" s="104"/>
-      <c r="L321" s="104"/>
-      <c r="M321" s="104"/>
-      <c r="N321" s="104"/>
-      <c r="O321" s="104"/>
-      <c r="P321" s="104"/>
-      <c r="Q321" s="104"/>
-      <c r="R321" s="104"/>
+      <c r="B321" s="105"/>
+      <c r="C321" s="105"/>
+      <c r="D321" s="105"/>
+      <c r="E321" s="105"/>
+      <c r="F321" s="105"/>
+      <c r="G321" s="105"/>
+      <c r="H321" s="105"/>
+      <c r="I321" s="105"/>
+      <c r="J321" s="105"/>
+      <c r="K321" s="105"/>
+      <c r="L321" s="105"/>
+      <c r="M321" s="105"/>
+      <c r="N321" s="105"/>
+      <c r="O321" s="105"/>
+      <c r="P321" s="105"/>
+      <c r="Q321" s="105"/>
+      <c r="R321" s="105"/>
     </row>
     <row r="322" spans="1:18">
-      <c r="A322" s="104" t="s">
+      <c r="A322" s="105" t="s">
         <v>836</v>
       </c>
-      <c r="B322" s="104"/>
-      <c r="C322" s="104"/>
-      <c r="D322" s="104"/>
-      <c r="E322" s="104"/>
-      <c r="F322" s="104"/>
-      <c r="G322" s="104"/>
-      <c r="H322" s="104"/>
-      <c r="I322" s="104"/>
-      <c r="J322" s="104"/>
-      <c r="K322" s="104"/>
-      <c r="L322" s="104"/>
-      <c r="M322" s="104"/>
-      <c r="N322" s="104"/>
-      <c r="O322" s="104"/>
-      <c r="P322" s="104"/>
-      <c r="Q322" s="104"/>
-      <c r="R322" s="104"/>
+      <c r="B322" s="105"/>
+      <c r="C322" s="105"/>
+      <c r="D322" s="105"/>
+      <c r="E322" s="105"/>
+      <c r="F322" s="105"/>
+      <c r="G322" s="105"/>
+      <c r="H322" s="105"/>
+      <c r="I322" s="105"/>
+      <c r="J322" s="105"/>
+      <c r="K322" s="105"/>
+      <c r="L322" s="105"/>
+      <c r="M322" s="105"/>
+      <c r="N322" s="105"/>
+      <c r="O322" s="105"/>
+      <c r="P322" s="105"/>
+      <c r="Q322" s="105"/>
+      <c r="R322" s="105"/>
     </row>
     <row r="323" spans="1:18">
-      <c r="A323" s="104" t="s">
+      <c r="A323" s="105" t="s">
         <v>837</v>
       </c>
-      <c r="B323" s="104"/>
-      <c r="C323" s="104"/>
-      <c r="D323" s="104"/>
-      <c r="E323" s="104"/>
-      <c r="F323" s="104"/>
-      <c r="G323" s="104"/>
-      <c r="H323" s="104"/>
-      <c r="I323" s="104"/>
-      <c r="J323" s="104"/>
-      <c r="K323" s="104"/>
-      <c r="L323" s="104"/>
-      <c r="M323" s="104"/>
-      <c r="N323" s="104"/>
-      <c r="O323" s="104"/>
-      <c r="P323" s="104"/>
-      <c r="Q323" s="104"/>
-      <c r="R323" s="104"/>
+      <c r="B323" s="105"/>
+      <c r="C323" s="105"/>
+      <c r="D323" s="105"/>
+      <c r="E323" s="105"/>
+      <c r="F323" s="105"/>
+      <c r="G323" s="105"/>
+      <c r="H323" s="105"/>
+      <c r="I323" s="105"/>
+      <c r="J323" s="105"/>
+      <c r="K323" s="105"/>
+      <c r="L323" s="105"/>
+      <c r="M323" s="105"/>
+      <c r="N323" s="105"/>
+      <c r="O323" s="105"/>
+      <c r="P323" s="105"/>
+      <c r="Q323" s="105"/>
+      <c r="R323" s="105"/>
     </row>
     <row r="324" spans="1:18">
-      <c r="A324" s="104" t="s">
+      <c r="A324" s="105" t="s">
         <v>838</v>
       </c>
-      <c r="B324" s="104"/>
-      <c r="C324" s="104"/>
-      <c r="D324" s="104"/>
-      <c r="E324" s="104"/>
-      <c r="F324" s="104"/>
-      <c r="G324" s="104"/>
-      <c r="H324" s="104"/>
-      <c r="I324" s="104"/>
-      <c r="J324" s="104"/>
-      <c r="K324" s="104"/>
-      <c r="L324" s="104"/>
-      <c r="M324" s="104"/>
-      <c r="N324" s="104"/>
-      <c r="O324" s="104"/>
-      <c r="P324" s="104"/>
-      <c r="Q324" s="104"/>
-      <c r="R324" s="104"/>
+      <c r="B324" s="105"/>
+      <c r="C324" s="105"/>
+      <c r="D324" s="105"/>
+      <c r="E324" s="105"/>
+      <c r="F324" s="105"/>
+      <c r="G324" s="105"/>
+      <c r="H324" s="105"/>
+      <c r="I324" s="105"/>
+      <c r="J324" s="105"/>
+      <c r="K324" s="105"/>
+      <c r="L324" s="105"/>
+      <c r="M324" s="105"/>
+      <c r="N324" s="105"/>
+      <c r="O324" s="105"/>
+      <c r="P324" s="105"/>
+      <c r="Q324" s="105"/>
+      <c r="R324" s="105"/>
     </row>
     <row r="325" spans="1:18">
-      <c r="A325" s="104" t="s">
+      <c r="A325" s="105" t="s">
         <v>839</v>
       </c>
-      <c r="B325" s="104"/>
-      <c r="C325" s="104"/>
-      <c r="D325" s="104"/>
-      <c r="E325" s="104"/>
-      <c r="F325" s="104"/>
-      <c r="G325" s="104"/>
-      <c r="H325" s="104"/>
-      <c r="I325" s="104"/>
-      <c r="J325" s="104"/>
-      <c r="K325" s="104"/>
-      <c r="L325" s="104"/>
-      <c r="M325" s="104"/>
-      <c r="N325" s="104"/>
-      <c r="O325" s="104"/>
-      <c r="P325" s="104"/>
-      <c r="Q325" s="104"/>
-      <c r="R325" s="104"/>
+      <c r="B325" s="105"/>
+      <c r="C325" s="105"/>
+      <c r="D325" s="105"/>
+      <c r="E325" s="105"/>
+      <c r="F325" s="105"/>
+      <c r="G325" s="105"/>
+      <c r="H325" s="105"/>
+      <c r="I325" s="105"/>
+      <c r="J325" s="105"/>
+      <c r="K325" s="105"/>
+      <c r="L325" s="105"/>
+      <c r="M325" s="105"/>
+      <c r="N325" s="105"/>
+      <c r="O325" s="105"/>
+      <c r="P325" s="105"/>
+      <c r="Q325" s="105"/>
+      <c r="R325" s="105"/>
     </row>
     <row r="326" spans="1:18">
-      <c r="A326" s="104" t="s">
+      <c r="A326" s="105" t="s">
         <v>840</v>
       </c>
-      <c r="B326" s="104"/>
-      <c r="C326" s="104"/>
-      <c r="D326" s="104"/>
-      <c r="E326" s="104"/>
-      <c r="F326" s="104"/>
-      <c r="G326" s="104"/>
-      <c r="H326" s="104"/>
-      <c r="I326" s="104"/>
-      <c r="J326" s="104"/>
-      <c r="K326" s="104"/>
-      <c r="L326" s="104"/>
-      <c r="M326" s="104"/>
-      <c r="N326" s="104"/>
-      <c r="O326" s="104"/>
-      <c r="P326" s="104"/>
-      <c r="Q326" s="104"/>
-      <c r="R326" s="104"/>
+      <c r="B326" s="105"/>
+      <c r="C326" s="105"/>
+      <c r="D326" s="105"/>
+      <c r="E326" s="105"/>
+      <c r="F326" s="105"/>
+      <c r="G326" s="105"/>
+      <c r="H326" s="105"/>
+      <c r="I326" s="105"/>
+      <c r="J326" s="105"/>
+      <c r="K326" s="105"/>
+      <c r="L326" s="105"/>
+      <c r="M326" s="105"/>
+      <c r="N326" s="105"/>
+      <c r="O326" s="105"/>
+      <c r="P326" s="105"/>
+      <c r="Q326" s="105"/>
+      <c r="R326" s="105"/>
     </row>
     <row r="327" spans="1:18">
-      <c r="A327" s="104" t="s">
+      <c r="A327" s="105" t="s">
         <v>841</v>
       </c>
-      <c r="B327" s="104"/>
-      <c r="C327" s="104"/>
-      <c r="D327" s="104"/>
-      <c r="E327" s="104"/>
-      <c r="F327" s="104"/>
-      <c r="G327" s="104"/>
-      <c r="H327" s="104"/>
-      <c r="I327" s="104"/>
-      <c r="J327" s="104"/>
-      <c r="K327" s="104"/>
-      <c r="L327" s="104"/>
-      <c r="M327" s="104"/>
-      <c r="N327" s="104"/>
-      <c r="O327" s="104"/>
-      <c r="P327" s="104"/>
-      <c r="Q327" s="104"/>
-      <c r="R327" s="104"/>
+      <c r="B327" s="105"/>
+      <c r="C327" s="105"/>
+      <c r="D327" s="105"/>
+      <c r="E327" s="105"/>
+      <c r="F327" s="105"/>
+      <c r="G327" s="105"/>
+      <c r="H327" s="105"/>
+      <c r="I327" s="105"/>
+      <c r="J327" s="105"/>
+      <c r="K327" s="105"/>
+      <c r="L327" s="105"/>
+      <c r="M327" s="105"/>
+      <c r="N327" s="105"/>
+      <c r="O327" s="105"/>
+      <c r="P327" s="105"/>
+      <c r="Q327" s="105"/>
+      <c r="R327" s="105"/>
     </row>
     <row r="328" spans="1:18">
-      <c r="A328" s="104" t="s">
+      <c r="A328" s="105" t="s">
         <v>842</v>
       </c>
-      <c r="B328" s="104"/>
-      <c r="C328" s="104"/>
-      <c r="D328" s="104"/>
-      <c r="E328" s="104"/>
-      <c r="F328" s="104"/>
-      <c r="G328" s="104"/>
-      <c r="H328" s="104"/>
-      <c r="I328" s="104"/>
-      <c r="J328" s="104"/>
-      <c r="K328" s="104"/>
-      <c r="L328" s="104"/>
-      <c r="M328" s="104"/>
-      <c r="N328" s="104"/>
-      <c r="O328" s="104"/>
-      <c r="P328" s="104"/>
-      <c r="Q328" s="104"/>
-      <c r="R328" s="104"/>
+      <c r="B328" s="105"/>
+      <c r="C328" s="105"/>
+      <c r="D328" s="105"/>
+      <c r="E328" s="105"/>
+      <c r="F328" s="105"/>
+      <c r="G328" s="105"/>
+      <c r="H328" s="105"/>
+      <c r="I328" s="105"/>
+      <c r="J328" s="105"/>
+      <c r="K328" s="105"/>
+      <c r="L328" s="105"/>
+      <c r="M328" s="105"/>
+      <c r="N328" s="105"/>
+      <c r="O328" s="105"/>
+      <c r="P328" s="105"/>
+      <c r="Q328" s="105"/>
+      <c r="R328" s="105"/>
     </row>
     <row r="329" spans="1:18">
-      <c r="A329" s="104" t="s">
+      <c r="A329" s="105" t="s">
         <v>843</v>
       </c>
-      <c r="B329" s="104"/>
-      <c r="C329" s="104"/>
-      <c r="D329" s="104"/>
-      <c r="E329" s="104"/>
-      <c r="F329" s="104"/>
-      <c r="G329" s="104"/>
-      <c r="H329" s="104"/>
-      <c r="I329" s="104"/>
-      <c r="J329" s="104"/>
-      <c r="K329" s="104"/>
-      <c r="L329" s="104"/>
-      <c r="M329" s="104"/>
-      <c r="N329" s="104"/>
-      <c r="O329" s="104"/>
-      <c r="P329" s="104"/>
-      <c r="Q329" s="104"/>
-      <c r="R329" s="104"/>
+      <c r="B329" s="105"/>
+      <c r="C329" s="105"/>
+      <c r="D329" s="105"/>
+      <c r="E329" s="105"/>
+      <c r="F329" s="105"/>
+      <c r="G329" s="105"/>
+      <c r="H329" s="105"/>
+      <c r="I329" s="105"/>
+      <c r="J329" s="105"/>
+      <c r="K329" s="105"/>
+      <c r="L329" s="105"/>
+      <c r="M329" s="105"/>
+      <c r="N329" s="105"/>
+      <c r="O329" s="105"/>
+      <c r="P329" s="105"/>
+      <c r="Q329" s="105"/>
+      <c r="R329" s="105"/>
     </row>
     <row r="330" spans="1:18">
-      <c r="A330" s="104" t="s">
+      <c r="A330" s="105" t="s">
         <v>844</v>
       </c>
-      <c r="B330" s="104"/>
-      <c r="C330" s="104"/>
-      <c r="D330" s="104"/>
-      <c r="E330" s="104"/>
-      <c r="F330" s="104"/>
-      <c r="G330" s="104"/>
-      <c r="H330" s="104"/>
-      <c r="I330" s="104"/>
-      <c r="J330" s="104"/>
-      <c r="K330" s="104"/>
-      <c r="L330" s="104"/>
-      <c r="M330" s="104"/>
-      <c r="N330" s="104"/>
-      <c r="O330" s="104"/>
-      <c r="P330" s="104"/>
-      <c r="Q330" s="104"/>
-      <c r="R330" s="104"/>
+      <c r="B330" s="105"/>
+      <c r="C330" s="105"/>
+      <c r="D330" s="105"/>
+      <c r="E330" s="105"/>
+      <c r="F330" s="105"/>
+      <c r="G330" s="105"/>
+      <c r="H330" s="105"/>
+      <c r="I330" s="105"/>
+      <c r="J330" s="105"/>
+      <c r="K330" s="105"/>
+      <c r="L330" s="105"/>
+      <c r="M330" s="105"/>
+      <c r="N330" s="105"/>
+      <c r="O330" s="105"/>
+      <c r="P330" s="105"/>
+      <c r="Q330" s="105"/>
+      <c r="R330" s="105"/>
     </row>
     <row r="331" spans="1:18">
-      <c r="A331" s="104" t="s">
+      <c r="A331" s="105" t="s">
         <v>845</v>
       </c>
-      <c r="B331" s="104"/>
-      <c r="C331" s="104"/>
-      <c r="D331" s="104"/>
-      <c r="E331" s="104"/>
-      <c r="F331" s="104"/>
-      <c r="G331" s="104"/>
-      <c r="H331" s="104"/>
-      <c r="I331" s="104"/>
-      <c r="J331" s="104"/>
-      <c r="K331" s="104"/>
-      <c r="L331" s="104"/>
-      <c r="M331" s="104"/>
-      <c r="N331" s="104"/>
-      <c r="O331" s="104"/>
-      <c r="P331" s="104"/>
-      <c r="Q331" s="104"/>
-      <c r="R331" s="104"/>
+      <c r="B331" s="105"/>
+      <c r="C331" s="105"/>
+      <c r="D331" s="105"/>
+      <c r="E331" s="105"/>
+      <c r="F331" s="105"/>
+      <c r="G331" s="105"/>
+      <c r="H331" s="105"/>
+      <c r="I331" s="105"/>
+      <c r="J331" s="105"/>
+      <c r="K331" s="105"/>
+      <c r="L331" s="105"/>
+      <c r="M331" s="105"/>
+      <c r="N331" s="105"/>
+      <c r="O331" s="105"/>
+      <c r="P331" s="105"/>
+      <c r="Q331" s="105"/>
+      <c r="R331" s="105"/>
     </row>
     <row r="332" spans="1:18">
-      <c r="A332" s="104" t="s">
+      <c r="A332" s="105" t="s">
         <v>846</v>
       </c>
-      <c r="B332" s="104"/>
-      <c r="C332" s="104"/>
-      <c r="D332" s="104"/>
-      <c r="E332" s="104"/>
-      <c r="F332" s="104"/>
-      <c r="G332" s="104"/>
-      <c r="H332" s="104"/>
-      <c r="I332" s="104"/>
-      <c r="J332" s="104"/>
-      <c r="K332" s="104"/>
-      <c r="L332" s="104"/>
-      <c r="M332" s="104"/>
-      <c r="N332" s="104"/>
-      <c r="O332" s="104"/>
-      <c r="P332" s="104"/>
-      <c r="Q332" s="104"/>
-      <c r="R332" s="104"/>
+      <c r="B332" s="105"/>
+      <c r="C332" s="105"/>
+      <c r="D332" s="105"/>
+      <c r="E332" s="105"/>
+      <c r="F332" s="105"/>
+      <c r="G332" s="105"/>
+      <c r="H332" s="105"/>
+      <c r="I332" s="105"/>
+      <c r="J332" s="105"/>
+      <c r="K332" s="105"/>
+      <c r="L332" s="105"/>
+      <c r="M332" s="105"/>
+      <c r="N332" s="105"/>
+      <c r="O332" s="105"/>
+      <c r="P332" s="105"/>
+      <c r="Q332" s="105"/>
+      <c r="R332" s="105"/>
     </row>
     <row r="333" spans="1:18">
-      <c r="A333" s="104" t="s">
+      <c r="A333" s="105" t="s">
         <v>847</v>
       </c>
-      <c r="B333" s="104"/>
-      <c r="C333" s="104"/>
-      <c r="D333" s="104"/>
-      <c r="E333" s="104"/>
-      <c r="F333" s="104"/>
-      <c r="G333" s="104"/>
-      <c r="H333" s="104"/>
-      <c r="I333" s="104"/>
-      <c r="J333" s="104"/>
-      <c r="K333" s="104"/>
-      <c r="L333" s="104"/>
-      <c r="M333" s="104"/>
-      <c r="N333" s="104"/>
-      <c r="O333" s="104"/>
-      <c r="P333" s="104"/>
-      <c r="Q333" s="104"/>
-      <c r="R333" s="104"/>
+      <c r="B333" s="105"/>
+      <c r="C333" s="105"/>
+      <c r="D333" s="105"/>
+      <c r="E333" s="105"/>
+      <c r="F333" s="105"/>
+      <c r="G333" s="105"/>
+      <c r="H333" s="105"/>
+      <c r="I333" s="105"/>
+      <c r="J333" s="105"/>
+      <c r="K333" s="105"/>
+      <c r="L333" s="105"/>
+      <c r="M333" s="105"/>
+      <c r="N333" s="105"/>
+      <c r="O333" s="105"/>
+      <c r="P333" s="105"/>
+      <c r="Q333" s="105"/>
+      <c r="R333" s="105"/>
     </row>
     <row r="334" spans="1:18">
-      <c r="A334" s="104" t="s">
+      <c r="A334" s="105" t="s">
         <v>848</v>
       </c>
-      <c r="B334" s="104"/>
-      <c r="C334" s="104"/>
-      <c r="D334" s="104"/>
-      <c r="E334" s="104"/>
-      <c r="F334" s="104"/>
-      <c r="G334" s="104"/>
-      <c r="H334" s="104"/>
-      <c r="I334" s="104"/>
-      <c r="J334" s="104"/>
-      <c r="K334" s="104"/>
-      <c r="L334" s="104"/>
-      <c r="M334" s="104"/>
-      <c r="N334" s="104"/>
-      <c r="O334" s="104"/>
-      <c r="P334" s="104"/>
-      <c r="Q334" s="104"/>
-      <c r="R334" s="104"/>
+      <c r="B334" s="105"/>
+      <c r="C334" s="105"/>
+      <c r="D334" s="105"/>
+      <c r="E334" s="105"/>
+      <c r="F334" s="105"/>
+      <c r="G334" s="105"/>
+      <c r="H334" s="105"/>
+      <c r="I334" s="105"/>
+      <c r="J334" s="105"/>
+      <c r="K334" s="105"/>
+      <c r="L334" s="105"/>
+      <c r="M334" s="105"/>
+      <c r="N334" s="105"/>
+      <c r="O334" s="105"/>
+      <c r="P334" s="105"/>
+      <c r="Q334" s="105"/>
+      <c r="R334" s="105"/>
     </row>
     <row r="335" spans="1:18">
-      <c r="A335" s="104" t="s">
+      <c r="A335" s="105" t="s">
         <v>849</v>
       </c>
-      <c r="B335" s="104"/>
-      <c r="C335" s="104"/>
-      <c r="D335" s="104"/>
-      <c r="E335" s="104"/>
-      <c r="F335" s="104"/>
-      <c r="G335" s="104"/>
-      <c r="H335" s="104"/>
-      <c r="I335" s="104"/>
-      <c r="J335" s="104"/>
-      <c r="K335" s="104"/>
-      <c r="L335" s="104"/>
-      <c r="M335" s="104"/>
-      <c r="N335" s="104"/>
-      <c r="O335" s="104"/>
-      <c r="P335" s="104"/>
-      <c r="Q335" s="104"/>
-      <c r="R335" s="104"/>
+      <c r="B335" s="105"/>
+      <c r="C335" s="105"/>
+      <c r="D335" s="105"/>
+      <c r="E335" s="105"/>
+      <c r="F335" s="105"/>
+      <c r="G335" s="105"/>
+      <c r="H335" s="105"/>
+      <c r="I335" s="105"/>
+      <c r="J335" s="105"/>
+      <c r="K335" s="105"/>
+      <c r="L335" s="105"/>
+      <c r="M335" s="105"/>
+      <c r="N335" s="105"/>
+      <c r="O335" s="105"/>
+      <c r="P335" s="105"/>
+      <c r="Q335" s="105"/>
+      <c r="R335" s="105"/>
     </row>
     <row r="336" spans="1:18">
-      <c r="A336" s="104" t="s">
+      <c r="A336" s="105" t="s">
         <v>850</v>
       </c>
-      <c r="B336" s="104"/>
-      <c r="C336" s="104"/>
-      <c r="D336" s="104"/>
-      <c r="E336" s="104"/>
-      <c r="F336" s="104"/>
-      <c r="G336" s="104"/>
-      <c r="H336" s="104"/>
-      <c r="I336" s="104"/>
-      <c r="J336" s="104"/>
-      <c r="K336" s="104"/>
-      <c r="L336" s="104"/>
-      <c r="M336" s="104"/>
-      <c r="N336" s="104"/>
-      <c r="O336" s="104"/>
-      <c r="P336" s="104"/>
-      <c r="Q336" s="104"/>
-      <c r="R336" s="104"/>
+      <c r="B336" s="105"/>
+      <c r="C336" s="105"/>
+      <c r="D336" s="105"/>
+      <c r="E336" s="105"/>
+      <c r="F336" s="105"/>
+      <c r="G336" s="105"/>
+      <c r="H336" s="105"/>
+      <c r="I336" s="105"/>
+      <c r="J336" s="105"/>
+      <c r="K336" s="105"/>
+      <c r="L336" s="105"/>
+      <c r="M336" s="105"/>
+      <c r="N336" s="105"/>
+      <c r="O336" s="105"/>
+      <c r="P336" s="105"/>
+      <c r="Q336" s="105"/>
+      <c r="R336" s="105"/>
     </row>
     <row r="337" spans="1:18">
-      <c r="A337" s="104" t="s">
+      <c r="A337" s="105" t="s">
         <v>851</v>
       </c>
-      <c r="B337" s="104"/>
-      <c r="C337" s="104"/>
-      <c r="D337" s="104"/>
-      <c r="E337" s="104"/>
-      <c r="F337" s="104"/>
-      <c r="G337" s="104"/>
-      <c r="H337" s="104"/>
-      <c r="I337" s="104"/>
-      <c r="J337" s="104"/>
-      <c r="K337" s="104"/>
-      <c r="L337" s="104"/>
-      <c r="M337" s="104"/>
-      <c r="N337" s="104"/>
-      <c r="O337" s="104"/>
-      <c r="P337" s="104"/>
-      <c r="Q337" s="104"/>
-      <c r="R337" s="104"/>
+      <c r="B337" s="105"/>
+      <c r="C337" s="105"/>
+      <c r="D337" s="105"/>
+      <c r="E337" s="105"/>
+      <c r="F337" s="105"/>
+      <c r="G337" s="105"/>
+      <c r="H337" s="105"/>
+      <c r="I337" s="105"/>
+      <c r="J337" s="105"/>
+      <c r="K337" s="105"/>
+      <c r="L337" s="105"/>
+      <c r="M337" s="105"/>
+      <c r="N337" s="105"/>
+      <c r="O337" s="105"/>
+      <c r="P337" s="105"/>
+      <c r="Q337" s="105"/>
+      <c r="R337" s="105"/>
     </row>
     <row r="338" spans="1:18">
-      <c r="A338" s="104"/>
-      <c r="B338" s="104"/>
-      <c r="C338" s="104"/>
-      <c r="D338" s="104"/>
-      <c r="E338" s="104"/>
-      <c r="F338" s="104"/>
-      <c r="G338" s="104"/>
-      <c r="H338" s="104"/>
-      <c r="I338" s="104"/>
-      <c r="J338" s="104"/>
-      <c r="K338" s="104"/>
-      <c r="L338" s="104"/>
-      <c r="M338" s="104"/>
-      <c r="N338" s="104"/>
-      <c r="O338" s="104"/>
-      <c r="P338" s="104"/>
-      <c r="Q338" s="104"/>
-      <c r="R338" s="104"/>
+      <c r="A338" s="105"/>
+      <c r="B338" s="105"/>
+      <c r="C338" s="105"/>
+      <c r="D338" s="105"/>
+      <c r="E338" s="105"/>
+      <c r="F338" s="105"/>
+      <c r="G338" s="105"/>
+      <c r="H338" s="105"/>
+      <c r="I338" s="105"/>
+      <c r="J338" s="105"/>
+      <c r="K338" s="105"/>
+      <c r="L338" s="105"/>
+      <c r="M338" s="105"/>
+      <c r="N338" s="105"/>
+      <c r="O338" s="105"/>
+      <c r="P338" s="105"/>
+      <c r="Q338" s="105"/>
+      <c r="R338" s="105"/>
     </row>
   </sheetData>
   <mergeCells count="22">
@@ -49863,13 +49864,13 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:H7"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="16.85546875" customWidth="1"/>
-    <col min="2" max="8" width="10.28515625" customWidth="1"/>
+    <col min="1" max="1" width="16.88671875" customWidth="1"/>
+    <col min="2" max="8" width="10.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="15.95">
+    <row r="1" spans="1:8" ht="28.8">
       <c r="A1" s="23" t="s">
         <v>97</v>
       </c>
@@ -49899,31 +49900,31 @@
       <c r="A2" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="B2" s="5">
+      <c r="B2" s="87">
         <f>RoadTransport!B62</f>
         <v>7478.7771151277711</v>
       </c>
-      <c r="C2" s="5">
+      <c r="C2" s="87">
         <f>RoadTransport!C62</f>
         <v>10008.121347837468</v>
       </c>
-      <c r="D2" s="5">
+      <c r="D2" s="87">
         <f>RoadTransport!D62</f>
         <v>33136386.12220085</v>
       </c>
-      <c r="E2" s="5">
+      <c r="E2" s="87">
         <f>RoadTransport!E62</f>
         <v>614964.80791135959</v>
       </c>
-      <c r="F2" s="5">
+      <c r="F2" s="87">
         <f>RoadTransport!F62</f>
         <v>22436.331345383314</v>
       </c>
-      <c r="G2" s="5">
+      <c r="G2" s="87">
         <f>RoadTransport!G62</f>
         <v>140725.84007944827</v>
       </c>
-      <c r="H2" s="5">
+      <c r="H2" s="87">
         <f>RoadTransport!H62</f>
         <v>0</v>
       </c>
@@ -49932,31 +49933,31 @@
       <c r="A3" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="B3" s="5">
+      <c r="B3" s="87">
         <f>RoadTransport!B63</f>
         <v>53.558376723330433</v>
       </c>
-      <c r="C3" s="5">
+      <c r="C3" s="87">
         <f>RoadTransport!C63</f>
         <v>71.671975937890622</v>
       </c>
-      <c r="D3" s="5">
+      <c r="D3" s="87">
         <f>RoadTransport!D63</f>
         <v>237302.30542540393</v>
       </c>
-      <c r="E3" s="5">
+      <c r="E3" s="87">
         <f>RoadTransport!E63</f>
         <v>4403.9976518466456</v>
       </c>
-      <c r="F3" s="5">
+      <c r="F3" s="87">
         <f>RoadTransport!F63</f>
         <v>160.67513016999132</v>
       </c>
-      <c r="G3" s="5">
+      <c r="G3" s="87">
         <f>RoadTransport!G63</f>
         <v>1007.7914399182463</v>
       </c>
-      <c r="H3" s="5">
+      <c r="H3" s="87">
         <f>RoadTransport!H63</f>
         <v>0</v>
       </c>
@@ -49965,26 +49966,26 @@
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="87">
         <v>0</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="87">
         <v>0</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="87">
         <v>0</v>
       </c>
-      <c r="E4" s="5">
+      <c r="E4" s="87">
         <f>AirFleet!AJ2</f>
         <v>358</v>
       </c>
-      <c r="F4">
+      <c r="F4" s="87">
         <v>0</v>
       </c>
-      <c r="G4" s="5">
+      <c r="G4" s="87">
         <v>0</v>
       </c>
-      <c r="H4" s="5">
+      <c r="H4" s="87">
         <v>0</v>
       </c>
     </row>
@@ -49992,26 +49993,26 @@
       <c r="A5" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="B5" s="4">
+      <c r="B5" s="87">
         <f>'Rail Pssgr'!D59</f>
         <v>384</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="87">
         <v>0</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="87">
         <v>0</v>
       </c>
-      <c r="E5" s="5">
+      <c r="E5" s="87">
         <v>0</v>
       </c>
-      <c r="F5">
+      <c r="F5" s="87">
         <v>0</v>
       </c>
-      <c r="G5" s="5">
+      <c r="G5" s="87">
         <v>0</v>
       </c>
-      <c r="H5" s="5">
+      <c r="H5" s="87">
         <v>0</v>
       </c>
     </row>
@@ -50019,25 +50020,25 @@
       <c r="A6" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="87">
         <v>0</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="87">
         <v>0</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="87">
         <v>0</v>
       </c>
-      <c r="E6" s="5">
+      <c r="E6" s="87">
         <v>0</v>
       </c>
-      <c r="F6">
+      <c r="F6" s="87">
         <v>0</v>
       </c>
-      <c r="G6" s="5">
+      <c r="G6" s="87">
         <v>0</v>
       </c>
-      <c r="H6" s="5">
+      <c r="H6" s="87">
         <v>0</v>
       </c>
     </row>
@@ -50045,31 +50046,31 @@
       <c r="A7" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="B7" s="4">
+      <c r="B7" s="87">
         <f>RoadTransport!B67</f>
         <v>29198.158486093394</v>
       </c>
-      <c r="C7" s="4">
+      <c r="C7" s="87">
         <f>RoadTransport!C67</f>
         <v>0</v>
       </c>
-      <c r="D7" s="5">
+      <c r="D7" s="87">
         <f>RoadTransport!D67</f>
         <v>5810433.5387326479</v>
       </c>
-      <c r="E7" s="4">
+      <c r="E7" s="87">
         <f>RoadTransport!E67</f>
         <v>0</v>
       </c>
-      <c r="F7" s="4">
+      <c r="F7" s="87">
         <f>RoadTransport!F67</f>
         <v>0</v>
       </c>
-      <c r="G7" s="5">
+      <c r="G7" s="87">
         <f>RoadTransport!G67</f>
         <v>0</v>
       </c>
-      <c r="H7" s="5">
+      <c r="H7" s="87">
         <f>RoadTransport!H67</f>
         <v>0</v>
       </c>
@@ -50084,14 +50085,14 @@
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <dimension ref="A1:H12"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="16.85546875" customWidth="1"/>
-    <col min="2" max="8" width="10.28515625" customWidth="1"/>
+    <col min="1" max="1" width="16.88671875" customWidth="1"/>
+    <col min="2" max="8" width="10.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="15.95">
+    <row r="1" spans="1:8" ht="28.8">
       <c r="A1" s="23" t="s">
         <v>97</v>
       </c>
@@ -50121,31 +50122,31 @@
       <c r="A2" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="B2" s="5">
+      <c r="B2" s="87">
         <f>RoadTransport!B71</f>
         <v>1577.2170528072124</v>
       </c>
-      <c r="C2" s="5">
+      <c r="C2" s="87">
         <f>RoadTransport!C71</f>
         <v>527.659115032454</v>
       </c>
-      <c r="D2" s="5">
+      <c r="D2" s="87">
         <f>RoadTransport!D71</f>
         <v>1747052.7753335293</v>
       </c>
-      <c r="E2" s="5">
+      <c r="E2" s="87">
         <f>RoadTransport!E71</f>
         <v>32422.84691009732</v>
       </c>
-      <c r="F2" s="5">
+      <c r="F2" s="87">
         <f>RoadTransport!F71</f>
         <v>0</v>
       </c>
-      <c r="G2" s="5">
+      <c r="G2" s="87">
         <f>RoadTransport!G71</f>
         <v>7419.5015885339199</v>
       </c>
-      <c r="H2" s="5">
+      <c r="H2" s="87">
         <f>RoadTransport!H71</f>
         <v>0</v>
       </c>
@@ -50154,31 +50155,31 @@
       <c r="A3" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="B3" s="5">
+      <c r="B3" s="87">
         <f>RoadTransport!B72</f>
         <v>547.48562872737784</v>
       </c>
-      <c r="C3" s="5">
+      <c r="C3" s="87">
         <f>RoadTransport!C72</f>
         <v>183.1617162857205</v>
       </c>
-      <c r="D3" s="5">
+      <c r="D3" s="87">
         <f>RoadTransport!D72</f>
         <v>606439.22497603227</v>
       </c>
-      <c r="E3" s="5">
+      <c r="E3" s="87">
         <f>RoadTransport!E72</f>
         <v>11254.660665830315</v>
       </c>
-      <c r="F3" s="5">
+      <c r="F3" s="87">
         <f>RoadTransport!F72</f>
         <v>0</v>
       </c>
-      <c r="G3" s="5">
+      <c r="G3" s="87">
         <f>RoadTransport!G72</f>
         <v>2575.467013124407</v>
       </c>
-      <c r="H3" s="5">
+      <c r="H3" s="87">
         <f>RoadTransport!H72</f>
         <v>0</v>
       </c>
@@ -50187,26 +50188,26 @@
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="87">
         <v>0</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="87">
         <v>0</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="87">
         <v>0</v>
       </c>
-      <c r="E4" s="4">
+      <c r="E4" s="87">
         <f>AirFleet!AJ3</f>
         <v>82</v>
       </c>
-      <c r="F4">
+      <c r="F4" s="87">
         <v>0</v>
       </c>
-      <c r="G4" s="5">
+      <c r="G4" s="87">
         <v>0</v>
       </c>
-      <c r="H4" s="5">
+      <c r="H4" s="87">
         <v>0</v>
       </c>
     </row>
@@ -50214,26 +50215,26 @@
       <c r="A5" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="87">
         <v>0</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="87">
         <v>0</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="87">
         <v>0</v>
       </c>
-      <c r="E5" s="5">
+      <c r="E5" s="87">
         <f>Rail!I39</f>
         <v>1998</v>
       </c>
-      <c r="F5">
+      <c r="F5" s="87">
         <v>0</v>
       </c>
-      <c r="G5" s="5">
+      <c r="G5" s="87">
         <v>0</v>
       </c>
-      <c r="H5" s="5">
+      <c r="H5" s="87">
         <v>0</v>
       </c>
     </row>
@@ -50241,26 +50242,26 @@
       <c r="A6" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="87">
         <v>0</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="87">
         <v>0</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="87">
         <v>0</v>
       </c>
-      <c r="E6" s="5">
+      <c r="E6" s="87">
         <f>Ships!C10</f>
         <v>382.92</v>
       </c>
-      <c r="F6">
+      <c r="F6" s="87">
         <v>0</v>
       </c>
-      <c r="G6" s="5">
+      <c r="G6" s="87">
         <v>0</v>
       </c>
-      <c r="H6" s="5">
+      <c r="H6" s="87">
         <v>0</v>
       </c>
     </row>
@@ -50268,27 +50269,72 @@
       <c r="A7" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="87">
         <v>0</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="87">
         <v>0</v>
       </c>
-      <c r="D7">
+      <c r="D7" s="87">
         <v>0</v>
       </c>
-      <c r="E7">
+      <c r="E7" s="87">
         <v>0</v>
       </c>
-      <c r="F7">
+      <c r="F7" s="87">
         <v>0</v>
       </c>
-      <c r="G7" s="5">
+      <c r="G7" s="87">
         <v>0</v>
       </c>
-      <c r="H7" s="5">
+      <c r="H7" s="87">
         <v>0</v>
       </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="B8" s="87"/>
+      <c r="C8" s="87"/>
+      <c r="D8" s="87"/>
+      <c r="E8" s="87"/>
+      <c r="F8" s="87"/>
+      <c r="G8" s="87"/>
+      <c r="H8" s="87"/>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="B9" s="87"/>
+      <c r="C9" s="87"/>
+      <c r="D9" s="87"/>
+      <c r="E9" s="87"/>
+      <c r="F9" s="87"/>
+      <c r="G9" s="87"/>
+      <c r="H9" s="87"/>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="B10" s="87"/>
+      <c r="C10" s="87"/>
+      <c r="D10" s="87"/>
+      <c r="E10" s="87"/>
+      <c r="F10" s="87"/>
+      <c r="G10" s="87"/>
+      <c r="H10" s="87"/>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="B11" s="87"/>
+      <c r="C11" s="87"/>
+      <c r="D11" s="87"/>
+      <c r="E11" s="87"/>
+      <c r="F11" s="87"/>
+      <c r="G11" s="87"/>
+      <c r="H11" s="87"/>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="B12" s="87"/>
+      <c r="C12" s="87"/>
+      <c r="D12" s="87"/>
+      <c r="E12" s="87"/>
+      <c r="F12" s="87"/>
+      <c r="G12" s="87"/>
+      <c r="H12" s="87"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -50455,13 +50501,36 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2CA6F3F9-54E8-42CE-BA1E-720513583380}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2CA6F3F9-54E8-42CE-BA1E-720513583380}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0111859B-CD30-4769-AFDE-679195CD6BDD}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0111859B-CD30-4769-AFDE-679195CD6BDD}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="79748b23-d81a-423e-9112-21109dc864e6"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{33C1B47E-950D-4DFF-9560-C2E26531F87C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{33C1B47E-950D-4DFF-9560-C2E26531F87C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/InputData/trans/SYVbT/Start Year Vehicles by Technology.xlsx
+++ b/InputData/trans/SYVbT/Start Year Vehicles by Technology.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rachel Goldstein\Desktop\EPS Models\Mexico EPS\InputData\trans\SYVbT\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Olivia Ashmoore\Documents\EPS_Models by Region\eps-mexico\InputData\trans\SYVbT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9ADCFEE3-EE4F-421D-9E7F-B8BB47F83F39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF67BB43-7868-42EA-92BA-F47C9CCA543F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="44145" yWindow="1230" windowWidth="22785" windowHeight="14115" firstSheet="2" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-90" yWindow="-90" windowWidth="19380" windowHeight="10260" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -4365,7 +4365,16 @@
     <xf numFmtId="0" fontId="49" fillId="2" borderId="0" xfId="73" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="0" xfId="73" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="36" borderId="21" xfId="73" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="60" fillId="36" borderId="0" xfId="73" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="37" borderId="0" xfId="73" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="73" applyFont="1"/>
@@ -4373,14 +4382,23 @@
     <xf numFmtId="0" fontId="57" fillId="35" borderId="23" xfId="73" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="0" xfId="73" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="60" fillId="36" borderId="21" xfId="73" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="37" borderId="0" xfId="73" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -4389,25 +4407,7 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
@@ -5664,9 +5664,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B38"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="73.109375" customWidth="1"/>
+    <col min="2" max="2" width="73.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -5849,15 +5849,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA9ECEC9-2D67-2F44-9D1D-E497A821C590}">
   <dimension ref="A1:AU81"/>
-  <sheetFormatPr defaultColWidth="10.88671875" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="10.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="30.88671875" style="69" customWidth="1"/>
-    <col min="2" max="2" width="11.109375" style="69" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.88671875" style="69"/>
-    <col min="4" max="4" width="13.6640625" style="69" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="11.109375" style="69" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="30.85546875" style="69" customWidth="1"/>
+    <col min="2" max="2" width="11.140625" style="69" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.85546875" style="69"/>
+    <col min="4" max="4" width="13.7109375" style="69" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="11.140625" style="69" bestFit="1" customWidth="1"/>
     <col min="7" max="8" width="11" style="69" bestFit="1" customWidth="1"/>
-    <col min="9" max="16384" width="10.88671875" style="69"/>
+    <col min="9" max="16384" width="10.85546875" style="69"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:47">
@@ -7457,12 +7457,11 @@
         <v>2.9494640303658694E-4</v>
       </c>
       <c r="D69" s="69">
-        <f t="shared" si="5"/>
-        <v>0.97655269722388449</v>
+        <f>1-SUM(B69:C69,E69:H69)</f>
+        <v>1.4676144350825204E-2</v>
       </c>
       <c r="E69" s="69">
-        <f t="shared" si="5"/>
-        <v>1.8123447126940927E-2</v>
+        <v>0.98</v>
       </c>
       <c r="G69" s="69">
         <f t="shared" si="5"/>
@@ -7513,11 +7512,11 @@
       </c>
       <c r="D71" s="5">
         <f t="shared" si="6"/>
-        <v>1747052.7753335293</v>
+        <v>26255.622243626291</v>
       </c>
       <c r="E71" s="5">
-        <f t="shared" si="6"/>
-        <v>32422.84691009732</v>
+        <f>$B46*E$69</f>
+        <v>1753220</v>
       </c>
       <c r="F71" s="5">
         <f t="shared" si="6"/>
@@ -7546,11 +7545,11 @@
       </c>
       <c r="D72" s="5">
         <f t="shared" si="6"/>
-        <v>606439.22497603227</v>
+        <v>9113.8856418624528</v>
       </c>
       <c r="E72" s="5">
-        <f t="shared" si="6"/>
-        <v>11254.660665830315</v>
+        <f>$B47*E$69</f>
+        <v>608580</v>
       </c>
       <c r="F72" s="84">
         <f t="shared" si="6"/>
@@ -7886,7 +7885,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{847F86A9-3044-3740-AA01-A50E40D8D85E}">
   <dimension ref="B26:F30"/>
-  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
   <sheetData>
     <row r="26" spans="2:6">
       <c r="B26" t="s">
@@ -7938,15 +7937,15 @@
     <tabColor theme="1" tint="0.34998626667073579"/>
   </sheetPr>
   <dimension ref="A2:AL409"/>
-  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="2" width="2" style="32" customWidth="1"/>
-    <col min="3" max="3" width="23.109375" style="32" customWidth="1"/>
+    <col min="3" max="3" width="23.140625" style="32" customWidth="1"/>
     <col min="4" max="4" width="33" style="32" bestFit="1" customWidth="1"/>
-    <col min="5" max="36" width="6.33203125" style="32" customWidth="1"/>
-    <col min="37" max="37" width="7.6640625" style="32" customWidth="1"/>
+    <col min="5" max="36" width="6.28515625" style="32" customWidth="1"/>
+    <col min="37" max="37" width="7.7109375" style="32" customWidth="1"/>
     <col min="38" max="38" width="2" style="32" customWidth="1"/>
-    <col min="39" max="16384" width="11.44140625" style="32"/>
+    <col min="39" max="16384" width="11.42578125" style="32"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:38">
@@ -8224,46 +8223,46 @@
       </c>
     </row>
     <row r="5" spans="1:38" ht="13.5" customHeight="1">
-      <c r="A5" s="93" t="s">
+      <c r="A5" s="89" t="s">
         <v>114</v>
       </c>
-      <c r="B5" s="93"/>
-      <c r="C5" s="93"/>
-      <c r="D5" s="93"/>
-      <c r="E5" s="93"/>
-      <c r="F5" s="93"/>
-      <c r="G5" s="93"/>
-      <c r="H5" s="93"/>
-      <c r="I5" s="93"/>
-      <c r="J5" s="93"/>
-      <c r="K5" s="93"/>
-      <c r="L5" s="93"/>
-      <c r="M5" s="93"/>
-      <c r="N5" s="93"/>
-      <c r="O5" s="93"/>
-      <c r="P5" s="93"/>
-      <c r="Q5" s="93"/>
-      <c r="R5" s="93"/>
-      <c r="S5" s="93"/>
-      <c r="T5" s="93"/>
-      <c r="U5" s="93"/>
-      <c r="V5" s="93"/>
-      <c r="W5" s="93"/>
-      <c r="X5" s="93"/>
-      <c r="Y5" s="93"/>
-      <c r="Z5" s="93"/>
-      <c r="AA5" s="93"/>
-      <c r="AB5" s="93"/>
-      <c r="AC5" s="93"/>
-      <c r="AD5" s="93"/>
-      <c r="AE5" s="93"/>
-      <c r="AF5" s="93"/>
-      <c r="AG5" s="93"/>
-      <c r="AH5" s="93"/>
-      <c r="AI5" s="93"/>
-      <c r="AJ5" s="93"/>
-      <c r="AK5" s="93"/>
-      <c r="AL5" s="93"/>
+      <c r="B5" s="89"/>
+      <c r="C5" s="89"/>
+      <c r="D5" s="89"/>
+      <c r="E5" s="89"/>
+      <c r="F5" s="89"/>
+      <c r="G5" s="89"/>
+      <c r="H5" s="89"/>
+      <c r="I5" s="89"/>
+      <c r="J5" s="89"/>
+      <c r="K5" s="89"/>
+      <c r="L5" s="89"/>
+      <c r="M5" s="89"/>
+      <c r="N5" s="89"/>
+      <c r="O5" s="89"/>
+      <c r="P5" s="89"/>
+      <c r="Q5" s="89"/>
+      <c r="R5" s="89"/>
+      <c r="S5" s="89"/>
+      <c r="T5" s="89"/>
+      <c r="U5" s="89"/>
+      <c r="V5" s="89"/>
+      <c r="W5" s="89"/>
+      <c r="X5" s="89"/>
+      <c r="Y5" s="89"/>
+      <c r="Z5" s="89"/>
+      <c r="AA5" s="89"/>
+      <c r="AB5" s="89"/>
+      <c r="AC5" s="89"/>
+      <c r="AD5" s="89"/>
+      <c r="AE5" s="89"/>
+      <c r="AF5" s="89"/>
+      <c r="AG5" s="89"/>
+      <c r="AH5" s="89"/>
+      <c r="AI5" s="89"/>
+      <c r="AJ5" s="89"/>
+      <c r="AK5" s="89"/>
+      <c r="AL5" s="89"/>
     </row>
     <row r="6" spans="1:38" ht="13.5" customHeight="1" thickBot="1"/>
     <row r="7" spans="1:38" s="62" customFormat="1" ht="22.5" customHeight="1" thickTop="1" thickBot="1">
@@ -8376,10 +8375,10 @@
     </row>
     <row r="8" spans="1:38" s="62" customFormat="1" ht="21" customHeight="1" thickTop="1">
       <c r="B8" s="61"/>
-      <c r="C8" s="94" t="s">
+      <c r="C8" s="90" t="s">
         <v>117</v>
       </c>
-      <c r="D8" s="94"/>
+      <c r="D8" s="90"/>
       <c r="E8" s="60">
         <f t="shared" ref="E8:AJ8" si="2">+E9+E14+E23+E18+E40+E42+E62+E75+E79+E82+E95+E102+E119+E121</f>
         <v>130</v>
@@ -13501,10 +13500,10 @@
       <c r="B93" s="55">
         <v>6</v>
       </c>
-      <c r="C93" s="95" t="s">
+      <c r="C93" s="92" t="s">
         <v>193</v>
       </c>
-      <c r="D93" s="95"/>
+      <c r="D93" s="92"/>
       <c r="E93" s="54"/>
       <c r="F93" s="54"/>
       <c r="G93" s="54"/>
@@ -15377,10 +15376,10 @@
     </row>
     <row r="129" spans="2:37" ht="21" customHeight="1">
       <c r="B129" s="61"/>
-      <c r="C129" s="89" t="s">
+      <c r="C129" s="91" t="s">
         <v>218</v>
       </c>
-      <c r="D129" s="89"/>
+      <c r="D129" s="91"/>
       <c r="E129" s="60">
         <f t="shared" ref="E129:AJ129" si="14">+E130+E134+E137+E139+E144+E158+E162+E164+E167+E173+E179+E190+E193+E198+E202+E213+E215+E217+E220+E225</f>
         <v>54</v>
@@ -20936,10 +20935,10 @@
     </row>
     <row r="228" spans="2:37" ht="21" customHeight="1">
       <c r="B228" s="61"/>
-      <c r="C228" s="89" t="s">
+      <c r="C228" s="91" t="s">
         <v>288</v>
       </c>
-      <c r="D228" s="89"/>
+      <c r="D228" s="91"/>
       <c r="E228" s="60">
         <f t="shared" ref="E228:AJ228" si="27">+E229+E231+E234+E237+E240+E242+E244+E247+E249+E251+E253+E255+E257+E268+E270+E275+E277+E279+E281+E289</f>
         <v>4</v>
@@ -24015,10 +24014,10 @@
     </row>
     <row r="291" spans="2:37" ht="21" customHeight="1">
       <c r="B291" s="61"/>
-      <c r="C291" s="89" t="s">
+      <c r="C291" s="91" t="s">
         <v>323</v>
       </c>
-      <c r="D291" s="89"/>
+      <c r="D291" s="91"/>
       <c r="E291" s="60"/>
       <c r="F291" s="60">
         <f t="shared" ref="F291:AJ291" si="31">+F292+F294+F296+F299+F301+F304+F306+F309+F315+F331+F335+F337+F346+F348+F351+F362+F365+F367+F370+F372+F375+F379+F384+F386+F390+F396</f>
@@ -30128,10 +30127,10 @@
     </row>
     <row r="403" spans="2:38" s="37" customFormat="1" ht="22.5" customHeight="1" thickTop="1" thickBot="1">
       <c r="B403" s="42"/>
-      <c r="C403" s="92" t="s">
+      <c r="C403" s="95" t="s">
         <v>419</v>
       </c>
-      <c r="D403" s="92"/>
+      <c r="D403" s="95"/>
       <c r="E403" s="40">
         <f t="shared" ref="E403:AK403" si="49">+E291+E228+E129+E8</f>
         <v>188</v>
@@ -30270,10 +30269,10 @@
       <c r="B404" s="35" t="s">
         <v>420</v>
       </c>
-      <c r="C404" s="91" t="s">
+      <c r="C404" s="94" t="s">
         <v>421</v>
       </c>
-      <c r="D404" s="91"/>
+      <c r="D404" s="94"/>
       <c r="AC404" s="36"/>
       <c r="AD404" s="36"/>
       <c r="AE404" s="36"/>
@@ -30287,28 +30286,28 @@
       <c r="B405" s="35" t="s">
         <v>422</v>
       </c>
-      <c r="C405" s="90" t="s">
+      <c r="C405" s="93" t="s">
         <v>423</v>
       </c>
-      <c r="D405" s="90"/>
+      <c r="D405" s="93"/>
     </row>
     <row r="406" spans="2:38" ht="13.5" customHeight="1">
       <c r="B406" s="35" t="s">
         <v>424</v>
       </c>
-      <c r="C406" s="90" t="s">
+      <c r="C406" s="93" t="s">
         <v>425</v>
       </c>
-      <c r="D406" s="90"/>
+      <c r="D406" s="93"/>
     </row>
     <row r="407" spans="2:38" ht="13.5" customHeight="1">
       <c r="B407" s="35" t="s">
         <v>426</v>
       </c>
-      <c r="C407" s="90" t="s">
+      <c r="C407" s="93" t="s">
         <v>427</v>
       </c>
-      <c r="D407" s="90"/>
+      <c r="D407" s="93"/>
     </row>
     <row r="408" spans="2:38" ht="13.5" customHeight="1">
       <c r="B408" s="34"/>
@@ -30317,11 +30316,80 @@
     <row r="409" spans="2:38" ht="13.5" customHeight="1"/>
   </sheetData>
   <mergeCells count="95">
-    <mergeCell ref="C42:D42"/>
-    <mergeCell ref="C62:D62"/>
-    <mergeCell ref="C75:D75"/>
-    <mergeCell ref="C79:D79"/>
-    <mergeCell ref="C102:D102"/>
+    <mergeCell ref="C228:D228"/>
+    <mergeCell ref="C268:D268"/>
+    <mergeCell ref="C309:D309"/>
+    <mergeCell ref="C306:D306"/>
+    <mergeCell ref="C292:D292"/>
+    <mergeCell ref="C291:D291"/>
+    <mergeCell ref="C244:D244"/>
+    <mergeCell ref="C270:D270"/>
+    <mergeCell ref="C296:D296"/>
+    <mergeCell ref="C294:D294"/>
+    <mergeCell ref="C304:D304"/>
+    <mergeCell ref="C301:D301"/>
+    <mergeCell ref="C299:D299"/>
+    <mergeCell ref="C234:D234"/>
+    <mergeCell ref="C229:D229"/>
+    <mergeCell ref="C407:D407"/>
+    <mergeCell ref="C406:D406"/>
+    <mergeCell ref="C405:D405"/>
+    <mergeCell ref="C337:D337"/>
+    <mergeCell ref="C335:D335"/>
+    <mergeCell ref="C351:D351"/>
+    <mergeCell ref="C348:D348"/>
+    <mergeCell ref="C346:D346"/>
+    <mergeCell ref="C404:D404"/>
+    <mergeCell ref="C403:D403"/>
+    <mergeCell ref="C384:D384"/>
+    <mergeCell ref="C379:D379"/>
+    <mergeCell ref="C372:D372"/>
+    <mergeCell ref="C370:D370"/>
+    <mergeCell ref="C367:D367"/>
+    <mergeCell ref="C365:D365"/>
+    <mergeCell ref="C375:D375"/>
+    <mergeCell ref="C362:D362"/>
+    <mergeCell ref="C396:D396"/>
+    <mergeCell ref="C390:D390"/>
+    <mergeCell ref="C386:D386"/>
+    <mergeCell ref="C394:D394"/>
+    <mergeCell ref="C315:D315"/>
+    <mergeCell ref="C331:D331"/>
+    <mergeCell ref="C242:D242"/>
+    <mergeCell ref="C289:D289"/>
+    <mergeCell ref="C281:D281"/>
+    <mergeCell ref="C279:D279"/>
+    <mergeCell ref="C277:D277"/>
+    <mergeCell ref="C275:D275"/>
+    <mergeCell ref="C257:D257"/>
+    <mergeCell ref="C255:D255"/>
+    <mergeCell ref="C253:D253"/>
+    <mergeCell ref="C251:D251"/>
+    <mergeCell ref="C247:D247"/>
+    <mergeCell ref="C249:D249"/>
+    <mergeCell ref="C285:D285"/>
+    <mergeCell ref="C287:D287"/>
+    <mergeCell ref="C231:D231"/>
+    <mergeCell ref="C237:D237"/>
+    <mergeCell ref="C240:D240"/>
+    <mergeCell ref="C167:D167"/>
+    <mergeCell ref="C202:D202"/>
+    <mergeCell ref="C213:D213"/>
+    <mergeCell ref="C215:D215"/>
+    <mergeCell ref="C217:D217"/>
+    <mergeCell ref="C173:D173"/>
+    <mergeCell ref="C179:D179"/>
+    <mergeCell ref="C190:D190"/>
+    <mergeCell ref="C193:D193"/>
+    <mergeCell ref="C198:D198"/>
+    <mergeCell ref="C196:D196"/>
+    <mergeCell ref="C220:D220"/>
+    <mergeCell ref="C225:D225"/>
+    <mergeCell ref="C130:D130"/>
+    <mergeCell ref="C134:D134"/>
+    <mergeCell ref="C137:D137"/>
+    <mergeCell ref="C139:D139"/>
+    <mergeCell ref="C144:D144"/>
     <mergeCell ref="C158:D158"/>
     <mergeCell ref="C162:D162"/>
     <mergeCell ref="C164:D164"/>
@@ -30338,80 +30406,11 @@
     <mergeCell ref="C40:D40"/>
     <mergeCell ref="C121:D121"/>
     <mergeCell ref="C93:D93"/>
-    <mergeCell ref="C130:D130"/>
-    <mergeCell ref="C134:D134"/>
-    <mergeCell ref="C137:D137"/>
-    <mergeCell ref="C139:D139"/>
-    <mergeCell ref="C144:D144"/>
-    <mergeCell ref="C231:D231"/>
-    <mergeCell ref="C237:D237"/>
-    <mergeCell ref="C240:D240"/>
-    <mergeCell ref="C167:D167"/>
-    <mergeCell ref="C202:D202"/>
-    <mergeCell ref="C213:D213"/>
-    <mergeCell ref="C215:D215"/>
-    <mergeCell ref="C217:D217"/>
-    <mergeCell ref="C173:D173"/>
-    <mergeCell ref="C179:D179"/>
-    <mergeCell ref="C190:D190"/>
-    <mergeCell ref="C193:D193"/>
-    <mergeCell ref="C198:D198"/>
-    <mergeCell ref="C196:D196"/>
-    <mergeCell ref="C220:D220"/>
-    <mergeCell ref="C315:D315"/>
-    <mergeCell ref="C331:D331"/>
-    <mergeCell ref="C242:D242"/>
-    <mergeCell ref="C289:D289"/>
-    <mergeCell ref="C281:D281"/>
-    <mergeCell ref="C279:D279"/>
-    <mergeCell ref="C277:D277"/>
-    <mergeCell ref="C275:D275"/>
-    <mergeCell ref="C257:D257"/>
-    <mergeCell ref="C255:D255"/>
-    <mergeCell ref="C253:D253"/>
-    <mergeCell ref="C251:D251"/>
-    <mergeCell ref="C247:D247"/>
-    <mergeCell ref="C249:D249"/>
-    <mergeCell ref="C285:D285"/>
-    <mergeCell ref="C287:D287"/>
-    <mergeCell ref="C375:D375"/>
-    <mergeCell ref="C362:D362"/>
-    <mergeCell ref="C396:D396"/>
-    <mergeCell ref="C390:D390"/>
-    <mergeCell ref="C386:D386"/>
-    <mergeCell ref="C394:D394"/>
-    <mergeCell ref="C407:D407"/>
-    <mergeCell ref="C406:D406"/>
-    <mergeCell ref="C405:D405"/>
-    <mergeCell ref="C337:D337"/>
-    <mergeCell ref="C335:D335"/>
-    <mergeCell ref="C351:D351"/>
-    <mergeCell ref="C348:D348"/>
-    <mergeCell ref="C346:D346"/>
-    <mergeCell ref="C404:D404"/>
-    <mergeCell ref="C403:D403"/>
-    <mergeCell ref="C384:D384"/>
-    <mergeCell ref="C379:D379"/>
-    <mergeCell ref="C372:D372"/>
-    <mergeCell ref="C370:D370"/>
-    <mergeCell ref="C367:D367"/>
-    <mergeCell ref="C365:D365"/>
-    <mergeCell ref="C225:D225"/>
-    <mergeCell ref="C228:D228"/>
-    <mergeCell ref="C268:D268"/>
-    <mergeCell ref="C309:D309"/>
-    <mergeCell ref="C306:D306"/>
-    <mergeCell ref="C292:D292"/>
-    <mergeCell ref="C291:D291"/>
-    <mergeCell ref="C244:D244"/>
-    <mergeCell ref="C270:D270"/>
-    <mergeCell ref="C296:D296"/>
-    <mergeCell ref="C294:D294"/>
-    <mergeCell ref="C304:D304"/>
-    <mergeCell ref="C301:D301"/>
-    <mergeCell ref="C299:D299"/>
-    <mergeCell ref="C234:D234"/>
-    <mergeCell ref="C229:D229"/>
+    <mergeCell ref="C42:D42"/>
+    <mergeCell ref="C62:D62"/>
+    <mergeCell ref="C75:D75"/>
+    <mergeCell ref="C79:D79"/>
+    <mergeCell ref="C102:D102"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.39370078740157483" right="0.39370078740157483" top="0.39370078740157483" bottom="0" header="0" footer="0"/>
@@ -30433,15 +30432,15 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A26:K40"/>
-  <sheetFormatPr defaultColWidth="10.88671875" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="10.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="24.44140625" customWidth="1"/>
-    <col min="2" max="2" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="24.42578125" customWidth="1"/>
+    <col min="2" max="2" width="7.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
-    <col min="4" max="10" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="10" width="7.42578125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="6.44140625" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="5.109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="5.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="26" spans="1:11">
@@ -30759,49 +30758,49 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:P59"/>
-  <sheetFormatPr defaultColWidth="10.88671875" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="10.85546875" defaultRowHeight="15"/>
   <cols>
     <col min="3" max="3" width="17" customWidth="1"/>
-    <col min="4" max="4" width="13.44140625" customWidth="1"/>
+    <col min="4" max="4" width="13.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="15.6">
-      <c r="A1" s="104" t="s">
+    <row r="1" spans="1:15" ht="15.75">
+      <c r="A1" s="96" t="s">
         <v>441</v>
       </c>
-      <c r="B1" s="104"/>
-      <c r="C1" s="104"/>
-      <c r="D1" s="104"/>
-      <c r="E1" s="104"/>
-      <c r="F1" s="104"/>
-      <c r="G1" s="104"/>
+      <c r="B1" s="96"/>
+      <c r="C1" s="96"/>
+      <c r="D1" s="96"/>
+      <c r="E1" s="96"/>
+      <c r="F1" s="96"/>
+      <c r="G1" s="96"/>
       <c r="H1" s="9"/>
-      <c r="I1" s="101" t="s">
+      <c r="I1" s="97" t="s">
         <v>442</v>
       </c>
-      <c r="J1" s="101"/>
-      <c r="K1" s="101"/>
-      <c r="L1" s="101"/>
-      <c r="M1" s="101"/>
-      <c r="N1" s="101"/>
-      <c r="O1" s="101"/>
-    </row>
-    <row r="2" spans="1:15" ht="15.6">
-      <c r="A2" s="104"/>
-      <c r="B2" s="104"/>
-      <c r="C2" s="104"/>
-      <c r="D2" s="104"/>
-      <c r="E2" s="104"/>
-      <c r="F2" s="104"/>
-      <c r="G2" s="104"/>
+      <c r="J1" s="97"/>
+      <c r="K1" s="97"/>
+      <c r="L1" s="97"/>
+      <c r="M1" s="97"/>
+      <c r="N1" s="97"/>
+      <c r="O1" s="97"/>
+    </row>
+    <row r="2" spans="1:15" ht="15.75">
+      <c r="A2" s="96"/>
+      <c r="B2" s="96"/>
+      <c r="C2" s="96"/>
+      <c r="D2" s="96"/>
+      <c r="E2" s="96"/>
+      <c r="F2" s="96"/>
+      <c r="G2" s="96"/>
       <c r="H2" s="9"/>
-      <c r="I2" s="101"/>
-      <c r="J2" s="101"/>
-      <c r="K2" s="101"/>
-      <c r="L2" s="101"/>
-      <c r="M2" s="101"/>
-      <c r="N2" s="101"/>
-      <c r="O2" s="101"/>
+      <c r="I2" s="97"/>
+      <c r="J2" s="97"/>
+      <c r="K2" s="97"/>
+      <c r="L2" s="97"/>
+      <c r="M2" s="97"/>
+      <c r="N2" s="97"/>
+      <c r="O2" s="97"/>
     </row>
     <row r="3" spans="1:15">
       <c r="A3" s="98" t="s">
@@ -30841,15 +30840,15 @@
       <c r="N4" s="98"/>
       <c r="O4" s="98"/>
     </row>
-    <row r="5" spans="1:15" ht="41.4">
-      <c r="A5" s="100" t="s">
+    <row r="5" spans="1:15" ht="38.25">
+      <c r="A5" s="99" t="s">
         <v>445</v>
       </c>
-      <c r="B5" s="100"/>
-      <c r="C5" s="100" t="s">
+      <c r="B5" s="99"/>
+      <c r="C5" s="99" t="s">
         <v>446</v>
       </c>
-      <c r="D5" s="100" t="s">
+      <c r="D5" s="99" t="s">
         <v>447</v>
       </c>
       <c r="E5" s="12" t="s">
@@ -30861,23 +30860,23 @@
       <c r="G5" s="12" t="s">
         <v>450</v>
       </c>
-      <c r="I5" s="100" t="s">
+      <c r="I5" s="99" t="s">
         <v>445</v>
       </c>
-      <c r="J5" s="100"/>
-      <c r="K5" s="100" t="s">
+      <c r="J5" s="99"/>
+      <c r="K5" s="99" t="s">
         <v>451</v>
       </c>
-      <c r="L5" s="100"/>
-      <c r="M5" s="100"/>
-      <c r="N5" s="100"/>
-      <c r="O5" s="100"/>
-    </row>
-    <row r="6" spans="1:15" ht="42.6">
-      <c r="A6" s="100"/>
-      <c r="B6" s="100"/>
-      <c r="C6" s="100"/>
-      <c r="D6" s="100"/>
+      <c r="L5" s="99"/>
+      <c r="M5" s="99"/>
+      <c r="N5" s="99"/>
+      <c r="O5" s="99"/>
+    </row>
+    <row r="6" spans="1:15" ht="40.5">
+      <c r="A6" s="99"/>
+      <c r="B6" s="99"/>
+      <c r="C6" s="99"/>
+      <c r="D6" s="99"/>
       <c r="E6" s="12" t="s">
         <v>452</v>
       </c>
@@ -30887,12 +30886,12 @@
       <c r="G6" s="12" t="s">
         <v>454</v>
       </c>
-      <c r="I6" s="100"/>
-      <c r="J6" s="100"/>
-      <c r="K6" s="100" t="s">
+      <c r="I6" s="99"/>
+      <c r="J6" s="99"/>
+      <c r="K6" s="99" t="s">
         <v>455</v>
       </c>
-      <c r="L6" s="100" t="s">
+      <c r="L6" s="99" t="s">
         <v>456</v>
       </c>
       <c r="M6" s="12" t="s">
@@ -30905,7 +30904,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="7" spans="1:15" ht="27.6">
+    <row r="7" spans="1:15" ht="25.5">
       <c r="A7" s="19">
         <v>2016</v>
       </c>
@@ -30930,10 +30929,10 @@
         <f>SUM(G8:G19)*1000</f>
         <v>1169544759</v>
       </c>
-      <c r="I7" s="100"/>
-      <c r="J7" s="100"/>
-      <c r="K7" s="100"/>
-      <c r="L7" s="100"/>
+      <c r="I7" s="99"/>
+      <c r="J7" s="99"/>
+      <c r="K7" s="99"/>
+      <c r="L7" s="99"/>
       <c r="M7" s="12" t="s">
         <v>458</v>
       </c>
@@ -31433,14 +31432,14 @@
       <c r="A20" s="14" t="s">
         <v>71</v>
       </c>
-      <c r="B20" s="99" t="s">
+      <c r="B20" s="100" t="s">
         <v>473</v>
       </c>
-      <c r="C20" s="99"/>
-      <c r="D20" s="99"/>
-      <c r="E20" s="99"/>
-      <c r="F20" s="99"/>
-      <c r="G20" s="99"/>
+      <c r="C20" s="100"/>
+      <c r="D20" s="100"/>
+      <c r="E20" s="100"/>
+      <c r="F20" s="100"/>
+      <c r="G20" s="100"/>
       <c r="I20" s="98" t="s">
         <v>472</v>
       </c>
@@ -31461,221 +31460,221 @@
         <v>7569.8</v>
       </c>
     </row>
-    <row r="21" spans="1:16" ht="15">
+    <row r="21" spans="1:16">
       <c r="A21" s="15" t="s">
         <v>474</v>
       </c>
-      <c r="B21" s="99" t="s">
+      <c r="B21" s="100" t="s">
         <v>475</v>
       </c>
-      <c r="C21" s="99"/>
-      <c r="D21" s="99"/>
-      <c r="E21" s="99"/>
-      <c r="F21" s="99"/>
-      <c r="G21" s="99"/>
-      <c r="I21" s="103" t="s">
+      <c r="C21" s="100"/>
+      <c r="D21" s="100"/>
+      <c r="E21" s="100"/>
+      <c r="F21" s="100"/>
+      <c r="G21" s="100"/>
+      <c r="I21" s="101" t="s">
         <v>71</v>
       </c>
-      <c r="J21" s="99" t="s">
+      <c r="J21" s="100" t="s">
         <v>476</v>
       </c>
-      <c r="K21" s="99"/>
-      <c r="L21" s="99"/>
-      <c r="M21" s="99"/>
-      <c r="N21" s="99"/>
-      <c r="O21" s="99"/>
-    </row>
-    <row r="22" spans="1:16" ht="15">
+      <c r="K21" s="100"/>
+      <c r="L21" s="100"/>
+      <c r="M21" s="100"/>
+      <c r="N21" s="100"/>
+      <c r="O21" s="100"/>
+    </row>
+    <row r="22" spans="1:16">
       <c r="A22" s="15" t="s">
         <v>477</v>
       </c>
-      <c r="B22" s="99" t="s">
+      <c r="B22" s="100" t="s">
         <v>478</v>
       </c>
-      <c r="C22" s="99"/>
-      <c r="D22" s="99"/>
-      <c r="E22" s="99"/>
-      <c r="F22" s="99"/>
-      <c r="G22" s="99"/>
-      <c r="I22" s="103"/>
-      <c r="J22" s="99" t="s">
+      <c r="C22" s="100"/>
+      <c r="D22" s="100"/>
+      <c r="E22" s="100"/>
+      <c r="F22" s="100"/>
+      <c r="G22" s="100"/>
+      <c r="I22" s="101"/>
+      <c r="J22" s="100" t="s">
         <v>479</v>
       </c>
-      <c r="K22" s="99"/>
-      <c r="L22" s="99"/>
-      <c r="M22" s="99"/>
-      <c r="N22" s="99"/>
-      <c r="O22" s="99"/>
-    </row>
-    <row r="23" spans="1:16" ht="15">
+      <c r="K22" s="100"/>
+      <c r="L22" s="100"/>
+      <c r="M22" s="100"/>
+      <c r="N22" s="100"/>
+      <c r="O22" s="100"/>
+    </row>
+    <row r="23" spans="1:16">
       <c r="A23" s="15" t="s">
         <v>480</v>
       </c>
-      <c r="B23" s="99" t="s">
+      <c r="B23" s="100" t="s">
         <v>481</v>
       </c>
-      <c r="C23" s="99"/>
-      <c r="D23" s="99"/>
-      <c r="E23" s="99"/>
-      <c r="F23" s="99"/>
-      <c r="G23" s="99"/>
+      <c r="C23" s="100"/>
+      <c r="D23" s="100"/>
+      <c r="E23" s="100"/>
+      <c r="F23" s="100"/>
+      <c r="G23" s="100"/>
       <c r="I23" s="15" t="s">
         <v>474</v>
       </c>
-      <c r="J23" s="99" t="s">
+      <c r="J23" s="100" t="s">
         <v>475</v>
       </c>
-      <c r="K23" s="99"/>
-      <c r="L23" s="99"/>
-      <c r="M23" s="99"/>
-      <c r="N23" s="99"/>
-      <c r="O23" s="99"/>
-    </row>
-    <row r="24" spans="1:16" ht="15">
+      <c r="K23" s="100"/>
+      <c r="L23" s="100"/>
+      <c r="M23" s="100"/>
+      <c r="N23" s="100"/>
+      <c r="O23" s="100"/>
+    </row>
+    <row r="24" spans="1:16">
       <c r="A24" s="15" t="s">
         <v>482</v>
       </c>
-      <c r="B24" s="99" t="s">
+      <c r="B24" s="100" t="s">
         <v>483</v>
       </c>
-      <c r="C24" s="99"/>
-      <c r="D24" s="99"/>
-      <c r="E24" s="99"/>
-      <c r="F24" s="99"/>
-      <c r="G24" s="99"/>
+      <c r="C24" s="100"/>
+      <c r="D24" s="100"/>
+      <c r="E24" s="100"/>
+      <c r="F24" s="100"/>
+      <c r="G24" s="100"/>
       <c r="I24" s="15" t="s">
         <v>477</v>
       </c>
-      <c r="J24" s="99" t="s">
+      <c r="J24" s="100" t="s">
         <v>484</v>
       </c>
-      <c r="K24" s="99"/>
-      <c r="L24" s="99"/>
-      <c r="M24" s="99"/>
-      <c r="N24" s="99"/>
-      <c r="O24" s="99"/>
-    </row>
-    <row r="25" spans="1:16" ht="15">
+      <c r="K24" s="100"/>
+      <c r="L24" s="100"/>
+      <c r="M24" s="100"/>
+      <c r="N24" s="100"/>
+      <c r="O24" s="100"/>
+    </row>
+    <row r="25" spans="1:16">
       <c r="A25" s="15" t="s">
         <v>485</v>
       </c>
-      <c r="B25" s="99" t="s">
+      <c r="B25" s="100" t="s">
         <v>486</v>
       </c>
-      <c r="C25" s="99"/>
-      <c r="D25" s="99"/>
-      <c r="E25" s="99"/>
-      <c r="F25" s="99"/>
-      <c r="G25" s="99"/>
-      <c r="I25" s="96"/>
-      <c r="J25" s="96"/>
+      <c r="C25" s="100"/>
+      <c r="D25" s="100"/>
+      <c r="E25" s="100"/>
+      <c r="F25" s="100"/>
+      <c r="G25" s="100"/>
+      <c r="I25" s="102"/>
+      <c r="J25" s="102"/>
     </row>
     <row r="26" spans="1:16">
-      <c r="A26" s="97" t="s">
+      <c r="A26" s="103" t="s">
         <v>487</v>
       </c>
-      <c r="B26" s="97"/>
-      <c r="I26" s="97" t="s">
+      <c r="B26" s="103"/>
+      <c r="I26" s="103" t="s">
         <v>487</v>
       </c>
-      <c r="J26" s="97"/>
+      <c r="J26" s="103"/>
     </row>
     <row r="28" spans="1:16">
-      <c r="A28" s="101" t="s">
+      <c r="A28" s="97" t="s">
         <v>488</v>
       </c>
-      <c r="B28" s="101"/>
-      <c r="C28" s="101"/>
-      <c r="D28" s="101"/>
-      <c r="E28" s="101"/>
-      <c r="F28" s="101"/>
-      <c r="G28" s="101"/>
-      <c r="I28" s="101" t="s">
+      <c r="B28" s="97"/>
+      <c r="C28" s="97"/>
+      <c r="D28" s="97"/>
+      <c r="E28" s="97"/>
+      <c r="F28" s="97"/>
+      <c r="G28" s="97"/>
+      <c r="I28" s="97" t="s">
         <v>489</v>
       </c>
-      <c r="J28" s="101"/>
-      <c r="K28" s="101"/>
-      <c r="L28" s="101"/>
-      <c r="M28" s="101"/>
-      <c r="N28" s="101"/>
-      <c r="O28" s="101"/>
-      <c r="P28" s="101"/>
+      <c r="J28" s="97"/>
+      <c r="K28" s="97"/>
+      <c r="L28" s="97"/>
+      <c r="M28" s="97"/>
+      <c r="N28" s="97"/>
+      <c r="O28" s="97"/>
+      <c r="P28" s="97"/>
     </row>
     <row r="29" spans="1:16">
-      <c r="A29" s="101"/>
-      <c r="B29" s="101"/>
-      <c r="C29" s="101"/>
-      <c r="D29" s="101"/>
-      <c r="E29" s="101"/>
-      <c r="F29" s="101"/>
-      <c r="G29" s="101"/>
-      <c r="I29" s="101"/>
-      <c r="J29" s="101"/>
-      <c r="K29" s="101"/>
-      <c r="L29" s="101"/>
-      <c r="M29" s="101"/>
-      <c r="N29" s="101"/>
-      <c r="O29" s="101"/>
-      <c r="P29" s="101"/>
+      <c r="A29" s="97"/>
+      <c r="B29" s="97"/>
+      <c r="C29" s="97"/>
+      <c r="D29" s="97"/>
+      <c r="E29" s="97"/>
+      <c r="F29" s="97"/>
+      <c r="G29" s="97"/>
+      <c r="I29" s="97"/>
+      <c r="J29" s="97"/>
+      <c r="K29" s="97"/>
+      <c r="L29" s="97"/>
+      <c r="M29" s="97"/>
+      <c r="N29" s="97"/>
+      <c r="O29" s="97"/>
+      <c r="P29" s="97"/>
     </row>
     <row r="30" spans="1:16">
-      <c r="A30" s="102" t="s">
+      <c r="A30" s="104" t="s">
         <v>490</v>
       </c>
-      <c r="B30" s="102"/>
-      <c r="C30" s="102"/>
-      <c r="D30" s="102"/>
-      <c r="E30" s="102"/>
-      <c r="F30" s="102"/>
-      <c r="G30" s="102"/>
-      <c r="I30" s="102" t="s">
+      <c r="B30" s="104"/>
+      <c r="C30" s="104"/>
+      <c r="D30" s="104"/>
+      <c r="E30" s="104"/>
+      <c r="F30" s="104"/>
+      <c r="G30" s="104"/>
+      <c r="I30" s="104" t="s">
         <v>491</v>
       </c>
-      <c r="J30" s="102"/>
-      <c r="K30" s="102"/>
-      <c r="L30" s="102"/>
-      <c r="M30" s="102"/>
-      <c r="N30" s="102"/>
-      <c r="O30" s="102"/>
-      <c r="P30" s="102"/>
+      <c r="J30" s="104"/>
+      <c r="K30" s="104"/>
+      <c r="L30" s="104"/>
+      <c r="M30" s="104"/>
+      <c r="N30" s="104"/>
+      <c r="O30" s="104"/>
+      <c r="P30" s="104"/>
     </row>
     <row r="31" spans="1:16">
-      <c r="A31" s="96"/>
-      <c r="B31" s="96"/>
-      <c r="C31" s="96"/>
-      <c r="D31" s="96"/>
-      <c r="E31" s="96"/>
-      <c r="F31" s="96"/>
-      <c r="G31" s="96"/>
-      <c r="I31" s="96"/>
-      <c r="J31" s="96"/>
-      <c r="K31" s="96"/>
-      <c r="L31" s="96"/>
-      <c r="M31" s="96"/>
-      <c r="N31" s="96"/>
-      <c r="O31" s="96"/>
-      <c r="P31" s="96"/>
-    </row>
-    <row r="32" spans="1:16" ht="41.4">
-      <c r="A32" s="100" t="s">
+      <c r="A31" s="102"/>
+      <c r="B31" s="102"/>
+      <c r="C31" s="102"/>
+      <c r="D31" s="102"/>
+      <c r="E31" s="102"/>
+      <c r="F31" s="102"/>
+      <c r="G31" s="102"/>
+      <c r="I31" s="102"/>
+      <c r="J31" s="102"/>
+      <c r="K31" s="102"/>
+      <c r="L31" s="102"/>
+      <c r="M31" s="102"/>
+      <c r="N31" s="102"/>
+      <c r="O31" s="102"/>
+      <c r="P31" s="102"/>
+    </row>
+    <row r="32" spans="1:16" ht="38.25">
+      <c r="A32" s="99" t="s">
         <v>445</v>
       </c>
-      <c r="B32" s="100"/>
-      <c r="C32" s="100" t="s">
+      <c r="B32" s="99"/>
+      <c r="C32" s="99" t="s">
         <v>492</v>
       </c>
-      <c r="D32" s="100"/>
-      <c r="E32" s="100"/>
-      <c r="F32" s="100"/>
-      <c r="G32" s="100"/>
-      <c r="I32" s="100" t="s">
+      <c r="D32" s="99"/>
+      <c r="E32" s="99"/>
+      <c r="F32" s="99"/>
+      <c r="G32" s="99"/>
+      <c r="I32" s="99" t="s">
         <v>445</v>
       </c>
-      <c r="J32" s="100"/>
+      <c r="J32" s="99"/>
       <c r="K32" s="12" t="s">
         <v>493</v>
       </c>
-      <c r="L32" s="100" t="s">
+      <c r="L32" s="99" t="s">
         <v>494</v>
       </c>
       <c r="M32" s="12" t="s">
@@ -31691,13 +31690,13 @@
         <v>495</v>
       </c>
     </row>
-    <row r="33" spans="1:16" ht="41.4">
-      <c r="A33" s="100"/>
-      <c r="B33" s="100"/>
-      <c r="C33" s="100" t="s">
+    <row r="33" spans="1:16" ht="38.25">
+      <c r="A33" s="99"/>
+      <c r="B33" s="99"/>
+      <c r="C33" s="99" t="s">
         <v>455</v>
       </c>
-      <c r="D33" s="100" t="s">
+      <c r="D33" s="99" t="s">
         <v>456</v>
       </c>
       <c r="E33" s="12" t="s">
@@ -31709,12 +31708,12 @@
       <c r="G33" s="12" t="s">
         <v>457</v>
       </c>
-      <c r="I33" s="100"/>
-      <c r="J33" s="100"/>
+      <c r="I33" s="99"/>
+      <c r="J33" s="99"/>
       <c r="K33" s="12" t="s">
         <v>496</v>
       </c>
-      <c r="L33" s="100"/>
+      <c r="L33" s="99"/>
       <c r="M33" s="12" t="s">
         <v>497</v>
       </c>
@@ -31728,11 +31727,11 @@
         <v>498</v>
       </c>
     </row>
-    <row r="34" spans="1:16" ht="27.6">
-      <c r="A34" s="100"/>
-      <c r="B34" s="100"/>
-      <c r="C34" s="100"/>
-      <c r="D34" s="100"/>
+    <row r="34" spans="1:16" ht="25.5">
+      <c r="A34" s="99"/>
+      <c r="B34" s="99"/>
+      <c r="C34" s="99"/>
+      <c r="D34" s="99"/>
       <c r="E34" s="12" t="s">
         <v>497</v>
       </c>
@@ -32292,7 +32291,7 @@
         <v>3378.7449999999999</v>
       </c>
     </row>
-    <row r="47" spans="1:16" ht="15">
+    <row r="47" spans="1:16">
       <c r="A47" s="98" t="s">
         <v>472</v>
       </c>
@@ -32315,69 +32314,69 @@
       <c r="I47" s="15" t="s">
         <v>474</v>
       </c>
-      <c r="J47" s="99" t="s">
+      <c r="J47" s="100" t="s">
         <v>475</v>
       </c>
-      <c r="K47" s="99"/>
-      <c r="L47" s="99"/>
-      <c r="M47" s="99"/>
-      <c r="N47" s="99"/>
-      <c r="O47" s="99"/>
-      <c r="P47" s="99"/>
-    </row>
-    <row r="48" spans="1:16" ht="15">
+      <c r="K47" s="100"/>
+      <c r="L47" s="100"/>
+      <c r="M47" s="100"/>
+      <c r="N47" s="100"/>
+      <c r="O47" s="100"/>
+      <c r="P47" s="100"/>
+    </row>
+    <row r="48" spans="1:16">
       <c r="A48" s="15" t="s">
         <v>474</v>
       </c>
-      <c r="B48" s="99" t="s">
+      <c r="B48" s="100" t="s">
         <v>475</v>
       </c>
-      <c r="C48" s="99"/>
-      <c r="D48" s="99"/>
-      <c r="E48" s="99"/>
-      <c r="F48" s="99"/>
-      <c r="G48" s="99"/>
+      <c r="C48" s="100"/>
+      <c r="D48" s="100"/>
+      <c r="E48" s="100"/>
+      <c r="F48" s="100"/>
+      <c r="G48" s="100"/>
       <c r="I48" s="15" t="s">
         <v>477</v>
       </c>
-      <c r="J48" s="99" t="s">
+      <c r="J48" s="100" t="s">
         <v>499</v>
       </c>
-      <c r="K48" s="99"/>
-      <c r="L48" s="99"/>
-      <c r="M48" s="99"/>
-      <c r="N48" s="99"/>
-      <c r="O48" s="99"/>
-      <c r="P48" s="99"/>
-    </row>
-    <row r="49" spans="1:10" ht="15">
+      <c r="K48" s="100"/>
+      <c r="L48" s="100"/>
+      <c r="M48" s="100"/>
+      <c r="N48" s="100"/>
+      <c r="O48" s="100"/>
+      <c r="P48" s="100"/>
+    </row>
+    <row r="49" spans="1:10">
       <c r="A49" s="15" t="s">
         <v>477</v>
       </c>
-      <c r="B49" s="99" t="s">
+      <c r="B49" s="100" t="s">
         <v>484</v>
       </c>
-      <c r="C49" s="99"/>
-      <c r="D49" s="99"/>
-      <c r="E49" s="99"/>
-      <c r="F49" s="99"/>
-      <c r="G49" s="99"/>
-      <c r="I49" s="96"/>
-      <c r="J49" s="96"/>
+      <c r="C49" s="100"/>
+      <c r="D49" s="100"/>
+      <c r="E49" s="100"/>
+      <c r="F49" s="100"/>
+      <c r="G49" s="100"/>
+      <c r="I49" s="102"/>
+      <c r="J49" s="102"/>
     </row>
     <row r="50" spans="1:10" ht="37.5" customHeight="1">
-      <c r="A50" s="96"/>
-      <c r="B50" s="96"/>
-      <c r="I50" s="97" t="s">
+      <c r="A50" s="102"/>
+      <c r="B50" s="102"/>
+      <c r="I50" s="103" t="s">
         <v>487</v>
       </c>
-      <c r="J50" s="97"/>
+      <c r="J50" s="103"/>
     </row>
     <row r="51" spans="1:10" ht="33" customHeight="1">
-      <c r="A51" s="97" t="s">
+      <c r="A51" s="103" t="s">
         <v>487</v>
       </c>
-      <c r="B51" s="97"/>
+      <c r="B51" s="103"/>
     </row>
     <row r="54" spans="1:10" ht="33.75" customHeight="1">
       <c r="C54" s="16" t="s">
@@ -32434,6 +32433,88 @@
     </row>
   </sheetData>
   <mergeCells count="93">
+    <mergeCell ref="A50:B50"/>
+    <mergeCell ref="I50:J50"/>
+    <mergeCell ref="A51:B51"/>
+    <mergeCell ref="A47:B47"/>
+    <mergeCell ref="J47:P47"/>
+    <mergeCell ref="B48:G48"/>
+    <mergeCell ref="J48:P48"/>
+    <mergeCell ref="B49:G49"/>
+    <mergeCell ref="I49:J49"/>
+    <mergeCell ref="A44:B44"/>
+    <mergeCell ref="I44:J44"/>
+    <mergeCell ref="A45:B45"/>
+    <mergeCell ref="I45:J45"/>
+    <mergeCell ref="A46:B46"/>
+    <mergeCell ref="I46:J46"/>
+    <mergeCell ref="A41:B41"/>
+    <mergeCell ref="I41:J41"/>
+    <mergeCell ref="A42:B42"/>
+    <mergeCell ref="I42:J42"/>
+    <mergeCell ref="A43:B43"/>
+    <mergeCell ref="I43:J43"/>
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="I38:J38"/>
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="A40:B40"/>
+    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="I35:J35"/>
+    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="I36:J36"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="I37:J37"/>
+    <mergeCell ref="A31:G31"/>
+    <mergeCell ref="I31:P31"/>
+    <mergeCell ref="A32:B34"/>
+    <mergeCell ref="C32:G32"/>
+    <mergeCell ref="I32:J33"/>
+    <mergeCell ref="L32:L33"/>
+    <mergeCell ref="C33:C34"/>
+    <mergeCell ref="D33:D34"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="I26:J26"/>
+    <mergeCell ref="A28:G29"/>
+    <mergeCell ref="I28:P29"/>
+    <mergeCell ref="A30:G30"/>
+    <mergeCell ref="I30:P30"/>
+    <mergeCell ref="B23:G23"/>
+    <mergeCell ref="J23:O23"/>
+    <mergeCell ref="B24:G24"/>
+    <mergeCell ref="J24:O24"/>
+    <mergeCell ref="B25:G25"/>
+    <mergeCell ref="I25:J25"/>
+    <mergeCell ref="B20:G20"/>
+    <mergeCell ref="I20:J20"/>
+    <mergeCell ref="B21:G21"/>
+    <mergeCell ref="I21:I22"/>
+    <mergeCell ref="J21:O21"/>
+    <mergeCell ref="B22:G22"/>
+    <mergeCell ref="J22:O22"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="I17:J17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="I18:J18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="I19:J19"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="I13:J13"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="I9:J9"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="I10:J10"/>
     <mergeCell ref="A1:G2"/>
     <mergeCell ref="I1:O2"/>
     <mergeCell ref="A3:G4"/>
@@ -32445,88 +32526,6 @@
     <mergeCell ref="K5:O5"/>
     <mergeCell ref="K6:K7"/>
     <mergeCell ref="L6:L7"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="I9:J9"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="I10:J10"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="I13:J13"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="I17:J17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="I18:J18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="I19:J19"/>
-    <mergeCell ref="B20:G20"/>
-    <mergeCell ref="I20:J20"/>
-    <mergeCell ref="B21:G21"/>
-    <mergeCell ref="I21:I22"/>
-    <mergeCell ref="J21:O21"/>
-    <mergeCell ref="B22:G22"/>
-    <mergeCell ref="J22:O22"/>
-    <mergeCell ref="B23:G23"/>
-    <mergeCell ref="J23:O23"/>
-    <mergeCell ref="B24:G24"/>
-    <mergeCell ref="J24:O24"/>
-    <mergeCell ref="B25:G25"/>
-    <mergeCell ref="I25:J25"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="I26:J26"/>
-    <mergeCell ref="A28:G29"/>
-    <mergeCell ref="I28:P29"/>
-    <mergeCell ref="A30:G30"/>
-    <mergeCell ref="I30:P30"/>
-    <mergeCell ref="A31:G31"/>
-    <mergeCell ref="I31:P31"/>
-    <mergeCell ref="A32:B34"/>
-    <mergeCell ref="C32:G32"/>
-    <mergeCell ref="I32:J33"/>
-    <mergeCell ref="L32:L33"/>
-    <mergeCell ref="C33:C34"/>
-    <mergeCell ref="D33:D34"/>
-    <mergeCell ref="I35:J35"/>
-    <mergeCell ref="A36:B36"/>
-    <mergeCell ref="I36:J36"/>
-    <mergeCell ref="A37:B37"/>
-    <mergeCell ref="I37:J37"/>
-    <mergeCell ref="A38:B38"/>
-    <mergeCell ref="I38:J38"/>
-    <mergeCell ref="A39:B39"/>
-    <mergeCell ref="I39:J39"/>
-    <mergeCell ref="A40:B40"/>
-    <mergeCell ref="I40:J40"/>
-    <mergeCell ref="A41:B41"/>
-    <mergeCell ref="I41:J41"/>
-    <mergeCell ref="A42:B42"/>
-    <mergeCell ref="I42:J42"/>
-    <mergeCell ref="A43:B43"/>
-    <mergeCell ref="I43:J43"/>
-    <mergeCell ref="A44:B44"/>
-    <mergeCell ref="I44:J44"/>
-    <mergeCell ref="A45:B45"/>
-    <mergeCell ref="I45:J45"/>
-    <mergeCell ref="A46:B46"/>
-    <mergeCell ref="I46:J46"/>
-    <mergeCell ref="A50:B50"/>
-    <mergeCell ref="I50:J50"/>
-    <mergeCell ref="A51:B51"/>
-    <mergeCell ref="A47:B47"/>
-    <mergeCell ref="J47:P47"/>
-    <mergeCell ref="B48:G48"/>
-    <mergeCell ref="J48:P48"/>
-    <mergeCell ref="B49:G49"/>
-    <mergeCell ref="I49:J49"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -32535,7 +32534,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A2:R338"/>
-  <sheetFormatPr defaultColWidth="10.88671875" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="10.85546875" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="22" bestFit="1" customWidth="1"/>
   </cols>
@@ -32585,7 +32584,7 @@
         <v>382.92</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="15.6">
+    <row r="13" spans="1:3" ht="15.75">
       <c r="A13" s="27" t="s">
         <v>512</v>
       </c>
@@ -32600,7 +32599,7 @@
         <v>514</v>
       </c>
     </row>
-    <row r="17" spans="1:18" ht="303.60000000000002">
+    <row r="17" spans="1:18" ht="293.25">
       <c r="A17" s="30" t="s">
         <v>515</v>
       </c>
@@ -49828,16 +49827,6 @@
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="A335:R335"/>
-    <mergeCell ref="A336:R336"/>
-    <mergeCell ref="A337:R337"/>
-    <mergeCell ref="A338:R338"/>
-    <mergeCell ref="A329:R329"/>
-    <mergeCell ref="A330:R330"/>
-    <mergeCell ref="A331:R331"/>
-    <mergeCell ref="A332:R332"/>
-    <mergeCell ref="A333:R333"/>
-    <mergeCell ref="A334:R334"/>
     <mergeCell ref="A328:R328"/>
     <mergeCell ref="A317:R317"/>
     <mergeCell ref="A318:R318"/>
@@ -49850,6 +49839,16 @@
     <mergeCell ref="A325:R325"/>
     <mergeCell ref="A326:R326"/>
     <mergeCell ref="A327:R327"/>
+    <mergeCell ref="A335:R335"/>
+    <mergeCell ref="A336:R336"/>
+    <mergeCell ref="A337:R337"/>
+    <mergeCell ref="A338:R338"/>
+    <mergeCell ref="A329:R329"/>
+    <mergeCell ref="A330:R330"/>
+    <mergeCell ref="A331:R331"/>
+    <mergeCell ref="A332:R332"/>
+    <mergeCell ref="A333:R333"/>
+    <mergeCell ref="A334:R334"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="B7" r:id="rId1" xr:uid="{CEA94E12-8357-E942-8D00-C6277BD2893C}"/>
@@ -49864,13 +49863,13 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:H7"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="16.88671875" customWidth="1"/>
-    <col min="2" max="8" width="10.33203125" customWidth="1"/>
+    <col min="1" max="1" width="16.85546875" customWidth="1"/>
+    <col min="2" max="8" width="10.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="28.8">
+    <row r="1" spans="1:8" ht="30">
       <c r="A1" s="23" t="s">
         <v>97</v>
       </c>
@@ -50086,13 +50085,13 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:H12"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="16.88671875" customWidth="1"/>
-    <col min="2" max="8" width="10.33203125" customWidth="1"/>
+    <col min="1" max="1" width="16.85546875" customWidth="1"/>
+    <col min="2" max="8" width="10.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="28.8">
+    <row r="1" spans="1:8" ht="30">
       <c r="A1" s="23" t="s">
         <v>97</v>
       </c>
@@ -50132,11 +50131,11 @@
       </c>
       <c r="D2" s="87">
         <f>RoadTransport!D71</f>
-        <v>1747052.7753335293</v>
+        <v>26255.622243626291</v>
       </c>
       <c r="E2" s="87">
         <f>RoadTransport!E71</f>
-        <v>32422.84691009732</v>
+        <v>1753220</v>
       </c>
       <c r="F2" s="87">
         <f>RoadTransport!F71</f>
@@ -50165,11 +50164,11 @@
       </c>
       <c r="D3" s="87">
         <f>RoadTransport!D72</f>
-        <v>606439.22497603227</v>
+        <v>9113.8856418624528</v>
       </c>
       <c r="E3" s="87">
         <f>RoadTransport!E72</f>
-        <v>11254.660665830315</v>
+        <v>608580</v>
       </c>
       <c r="F3" s="87">
         <f>RoadTransport!F72</f>
@@ -50342,15 +50341,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009A9DAB439B36DB4795F39C4E722C7BC4" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="44674c89fa9bc5e97a878a6680c46188">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="79748b23-d81a-423e-9112-21109dc864e6" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="447839a363ea5a12024b5bf1ab53ed90" ns2:_="">
     <xsd:import namespace="79748b23-d81a-423e-9112-21109dc864e6"/>
@@ -50494,6 +50484,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
@@ -50501,14 +50500,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2CA6F3F9-54E8-42CE-BA1E-720513583380}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0111859B-CD30-4769-AFDE-679195CD6BDD}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -50526,6 +50517,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2CA6F3F9-54E8-42CE-BA1E-720513583380}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{33C1B47E-950D-4DFF-9560-C2E26531F87C}">
   <ds:schemaRefs>
